--- a/models/deepseek-v4.1-flash/deepseek-v4.1-flash-analysis.xlsx
+++ b/models/deepseek-v4.1-flash/deepseek-v4.1-flash-analysis.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="Rcda6aaa74bce4cbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="Rf69eecd78ea44d9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R1d9b7ffae8a34ab1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="R212b10e90e21422f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,13 +14,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="8">
     <x:numFmt numFmtId="200" formatCode="0.##"/>
     <x:numFmt numFmtId="201" formatCode="0.0000"/>
     <x:numFmt numFmtId="202" formatCode="#,##0.####"/>
     <x:numFmt numFmtId="203" formatCode="0.000000"/>
+    <x:numFmt numFmtId="204" formatCode="0.0%"/>
+    <x:numFmt numFmtId="205" formatCode="0.000"/>
+    <x:numFmt numFmtId="206" formatCode="0.00%"/>
+    <x:numFmt numFmtId="207" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -46,8 +50,14 @@
       <x:color rgb="FF666666"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -67,6 +77,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8EEF5"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -104,7 +129,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="46">
+  <x:cellXfs count="59">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -191,10 +216,71 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
+  <x:dxfs count="2">
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FFA32020"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE9E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FFA32020"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE9E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
 </x:styleSheet>
 </file>
 
@@ -6237,6 +6323,785 @@
       <x:c r="O132" s="29"/>
       <x:c r="P132" s="29"/>
     </x:row>
+    <x:row r="135" ht="23" customHeight="1">
+      <x:c r="A135" s="46" t="str">
+        <x:v>PD 带宽争用耗时评估</x:v>
+      </x:c>
+      <x:c r="B135" s="29"/>
+      <x:c r="C135" s="29"/>
+      <x:c r="D135" s="29"/>
+      <x:c r="E135" s="29"/>
+      <x:c r="F135" s="29"/>
+      <x:c r="G135" s="29"/>
+      <x:c r="H135" s="29"/>
+      <x:c r="I135" s="29"/>
+      <x:c r="J135" s="29"/>
+      <x:c r="K135" s="29"/>
+      <x:c r="L135" s="29"/>
+    </x:row>
+    <x:row r="136" ht="23" customHeight="1">
+      <x:c r="A136" s="29" t="str">
+        <x:v>Prefill 当前表参数；100 GB/s 为归一化示例。所列事件的带宽项，不等于完整 forward 耗时。</x:v>
+      </x:c>
+      <x:c r="B136" s="29"/>
+      <x:c r="C136" s="29"/>
+      <x:c r="D136" s="29"/>
+      <x:c r="E136" s="29"/>
+      <x:c r="F136" s="29"/>
+      <x:c r="G136" s="29"/>
+      <x:c r="H136" s="29"/>
+      <x:c r="I136" s="29"/>
+      <x:c r="J136" s="29"/>
+      <x:c r="K136" s="29"/>
+      <x:c r="L136" s="29"/>
+    </x:row>
+    <x:row r="137" ht="38" customHeight="1">
+      <x:c r="A137" s="49" t="str">
+        <x:v>带宽降幅</x:v>
+      </x:c>
+      <x:c r="B137" s="49" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="C137" s="49" t="str">
+        <x:v>争用覆盖率</x:v>
+      </x:c>
+      <x:c r="D137" s="49" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="E137" s="49" t="str">
+        <x:v>基线 forward ms</x:v>
+      </x:c>
+      <x:c r="F137" s="49" t="str">
+        <x:v>实测输入</x:v>
+      </x:c>
+      <x:c r="G137" s="49" t="str">
+        <x:v>默认带宽 GB/s</x:v>
+      </x:c>
+      <x:c r="H137" s="49" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="I137" s="29"/>
+      <x:c r="J137" s="29"/>
+      <x:c r="K137" s="29"/>
+      <x:c r="L137" s="29"/>
+    </x:row>
+    <x:row r="138" ht="23" customHeight="1">
+      <x:c r="A138" s="29"/>
+      <x:c r="B138" s="51" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="C138" s="29"/>
+      <x:c r="D138" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E138" s="29"/>
+      <x:c r="F138" s="52"/>
+      <x:c r="G138" s="29"/>
+      <x:c r="H138" s="52" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I138" s="29"/>
+      <x:c r="J138" s="29"/>
+      <x:c r="K138" s="29"/>
+      <x:c r="L138" s="29"/>
+    </x:row>
+    <x:row r="139" ht="38" customHeight="1">
+      <x:c r="A139" s="49" t="str">
+        <x:v>通信基线 ms</x:v>
+      </x:c>
+      <x:c r="B139" s="49" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="C139" s="49" t="str">
+        <x:v>通信争用后 ms</x:v>
+      </x:c>
+      <x:c r="D139" s="49" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="E139" s="49" t="str">
+        <x:v>forward 增量 ms</x:v>
+      </x:c>
+      <x:c r="F139" s="49" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="G139" s="49" t="str">
+        <x:v>forward 新耗时 ms</x:v>
+      </x:c>
+      <x:c r="H139" s="49" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="I139" s="49" t="str">
+        <x:v>forward 增幅</x:v>
+      </x:c>
+      <x:c r="J139" s="49" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="K139" s="49" t="str">
+        <x:v>输入状态</x:v>
+      </x:c>
+      <x:c r="L139" s="49" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="23" customHeight="1">
+      <x:c r="A140" s="53"/>
+      <x:c r="B140" s="53" t="n">
+        <x:f>SUM(G144:G155)</x:f>
+        <x:v>267.39184624</x:v>
+      </x:c>
+      <x:c r="C140" s="53"/>
+      <x:c r="D140" s="53" t="n">
+        <x:f>SUM(H144:H155)</x:f>
+        <x:v>297.1020513777778</x:v>
+      </x:c>
+      <x:c r="E140" s="53"/>
+      <x:c r="F140" s="53" t="n">
+        <x:f>SUM(K144:K155)</x:f>
+        <x:v>29.710205137777784</x:v>
+      </x:c>
+      <x:c r="G140" s="53"/>
+      <x:c r="H140" s="53" t="str">
+        <x:f>IF(AND(ISNUMBER($F$138),$F$138&gt;0,$F$138&gt;=SUMPRODUCT(G144:G155,J144:J155)),$F$138+F140,"")</x:f>
+      </x:c>
+      <x:c r="I140" s="53"/>
+      <x:c r="J140" s="54" t="str">
+        <x:f>IF(AND(ISNUMBER($F$138),$F$138&gt;0,$F$138&gt;=SUMPRODUCT(G144:G155,J144:J155)),F140/$F$138,"")</x:f>
+      </x:c>
+      <x:c r="K140" s="53"/>
+      <x:c r="L140" s="53" t="str">
+        <x:f>IF($F$138="","待填基线",IF(AND(ISNUMBER($F$138),$F$138&gt;0,$F$138&gt;=SUMPRODUCT(G144:G155,J144:J155)),"已填基线","基线/暴露不一致"))</x:f>
+        <x:v>待填基线</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" ht="23" customHeight="1">
+      <x:c r="A141" s="29" t="str">
+        <x:v>共享比例=0 表示独立链路；暴露系数=0 表示增量完全隐藏。默认均为 1，降幅只作用于带宽项。</x:v>
+      </x:c>
+      <x:c r="B141" s="29"/>
+      <x:c r="C141" s="29"/>
+      <x:c r="D141" s="29"/>
+      <x:c r="E141" s="29"/>
+      <x:c r="F141" s="29"/>
+      <x:c r="G141" s="29"/>
+      <x:c r="H141" s="29"/>
+      <x:c r="I141" s="29"/>
+      <x:c r="J141" s="29"/>
+      <x:c r="K141" s="29"/>
+      <x:c r="L141" s="29"/>
+    </x:row>
+    <x:row r="142" ht="23" customHeight="1">
+      <x:c r="A142" s="29" t="str">
+        <x:v>V4.1 为 PD 条件评估；旧 KV 规划与新 main 的端到端迁移可用性未在本次验证。</x:v>
+      </x:c>
+      <x:c r="B142" s="29"/>
+      <x:c r="C142" s="29"/>
+      <x:c r="D142" s="29"/>
+      <x:c r="E142" s="29"/>
+      <x:c r="F142" s="29"/>
+      <x:c r="G142" s="29"/>
+      <x:c r="H142" s="29"/>
+      <x:c r="I142" s="29"/>
+      <x:c r="J142" s="29"/>
+      <x:c r="K142" s="29"/>
+      <x:c r="L142" s="29"/>
+    </x:row>
+    <x:row r="143" ht="38" customHeight="1">
+      <x:c r="A143" s="49" t="str">
+        <x:v>并行域</x:v>
+      </x:c>
+      <x:c r="B143" s="49" t="str">
+        <x:v>模块</x:v>
+      </x:c>
+      <x:c r="C143" s="49" t="str">
+        <x:v>通信事件</x:v>
+      </x:c>
+      <x:c r="D143" s="49" t="str">
+        <x:v>GB/Rank/Step</x:v>
+      </x:c>
+      <x:c r="E143" s="49" t="str">
+        <x:v>有效带宽 GB/s</x:v>
+      </x:c>
+      <x:c r="F143" s="49" t="str">
+        <x:v>共享比例</x:v>
+      </x:c>
+      <x:c r="G143" s="49" t="str">
+        <x:v>基线带宽项 ms</x:v>
+      </x:c>
+      <x:c r="H143" s="49" t="str">
+        <x:v>争用后带宽项 ms</x:v>
+      </x:c>
+      <x:c r="I143" s="49" t="str">
+        <x:v>通信增量 ms</x:v>
+      </x:c>
+      <x:c r="J143" s="49" t="str">
+        <x:v>暴露系数</x:v>
+      </x:c>
+      <x:c r="K143" s="49" t="str">
+        <x:v>forward 增量 ms</x:v>
+      </x:c>
+      <x:c r="L143" s="49" t="str">
+        <x:v>公式口径</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" ht="23" customHeight="1">
+      <x:c r="A144" s="29" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B144" s="29" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C144" s="29" t="str">
+        <x:v>逐层输入</x:v>
+      </x:c>
+      <x:c r="D144" s="33" t="n">
+        <x:f>(K121*2^20)/1e9</x:f>
+        <x:v>5.8720256</x:v>
+      </x:c>
+      <x:c r="E144" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F144" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G144" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E144),E144&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F144),F144&gt;=0,F144&lt;=1,ISNUMBER(J144),J144&gt;=0,J144&lt;=1),D144/E144*1000,NA())</x:f>
+        <x:v>58.720256</x:v>
+      </x:c>
+      <x:c r="H144" s="33" t="n">
+        <x:f>G144+I144</x:f>
+        <x:v>65.24472888888889</x:v>
+      </x:c>
+      <x:c r="I144" s="33" t="n">
+        <x:f>G144*F144*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>6.524472888888889</x:v>
+      </x:c>
+      <x:c r="J144" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K144" s="33" t="n">
+        <x:f>I144*J144</x:f>
+        <x:v>6.524472888888889</x:v>
+      </x:c>
+      <x:c r="L144" s="29" t="str">
+        <x:v>原通信行 121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="23" customHeight="1">
+      <x:c r="A145" s="29" t="str">
+        <x:v>DSA CP</x:v>
+      </x:c>
+      <x:c r="B145" s="29" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C145" s="29" t="str">
+        <x:v>Token/Head 交换</x:v>
+      </x:c>
+      <x:c r="D145" s="33" t="n">
+        <x:f>(K122*2^20)/1e9</x:f>
+        <x:v>4.69762048</x:v>
+      </x:c>
+      <x:c r="E145" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F145" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G145" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E145),E145&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F145),F145&gt;=0,F145&lt;=1,ISNUMBER(J145),J145&gt;=0,J145&lt;=1),D145/E145*1000,NA())</x:f>
+        <x:v>46.976204800000005</x:v>
+      </x:c>
+      <x:c r="H145" s="33" t="n">
+        <x:f>G145+I145</x:f>
+        <x:v>52.19578311111112</x:v>
+      </x:c>
+      <x:c r="I145" s="33" t="n">
+        <x:f>G145*F145*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>5.219578311111111</x:v>
+      </x:c>
+      <x:c r="J145" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K145" s="33" t="n">
+        <x:f>I145*J145</x:f>
+        <x:v>5.219578311111111</x:v>
+      </x:c>
+      <x:c r="L145" s="29" t="str">
+        <x:v>原通信行 122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="23" customHeight="1">
+      <x:c r="A146" s="29" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B146" s="29" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C146" s="29" t="str">
+        <x:v>O Proj 后</x:v>
+      </x:c>
+      <x:c r="D146" s="33" t="n">
+        <x:f>(K123*2^20)/1e9</x:f>
+        <x:v>5.8720256</x:v>
+      </x:c>
+      <x:c r="E146" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F146" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G146" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E146),E146&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F146),F146&gt;=0,F146&lt;=1,ISNUMBER(J146),J146&gt;=0,J146&lt;=1),D146/E146*1000,NA())</x:f>
+        <x:v>58.720256</x:v>
+      </x:c>
+      <x:c r="H146" s="33" t="n">
+        <x:f>G146+I146</x:f>
+        <x:v>65.24472888888889</x:v>
+      </x:c>
+      <x:c r="I146" s="33" t="n">
+        <x:f>G146*F146*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>6.524472888888889</x:v>
+      </x:c>
+      <x:c r="J146" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K146" s="33" t="n">
+        <x:f>I146*J146</x:f>
+        <x:v>6.524472888888889</x:v>
+      </x:c>
+      <x:c r="L146" s="29" t="str">
+        <x:v>原通信行 123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="23" customHeight="1">
+      <x:c r="A147" s="29" t="str">
+        <x:v>Attention TP</x:v>
+      </x:c>
+      <x:c r="B147" s="29" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C147" s="29" t="str">
+        <x:v>非 SP 输出</x:v>
+      </x:c>
+      <x:c r="D147" s="33" t="n">
+        <x:f>(K124*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E147" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F147" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G147" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E147),E147&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F147),F147&gt;=0,F147&lt;=1,ISNUMBER(J147),J147&gt;=0,J147&lt;=1),D147/E147*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H147" s="33" t="n">
+        <x:f>G147+I147</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I147" s="33" t="n">
+        <x:f>G147*F147*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J147" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K147" s="33" t="n">
+        <x:f>I147*J147</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L147" s="29" t="str">
+        <x:v>原通信行 124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="23" customHeight="1">
+      <x:c r="A148" s="29" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B148" s="29" t="str">
+        <x:v>Model Output</x:v>
+      </x:c>
+      <x:c r="C148" s="29" t="str">
+        <x:v>最终 Hidden</x:v>
+      </x:c>
+      <x:c r="D148" s="33" t="n">
+        <x:f>(K125*2^20)/1e9</x:f>
+        <x:v>0.14680064</x:v>
+      </x:c>
+      <x:c r="E148" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F148" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G148" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E148),E148&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F148),F148&gt;=0,F148&lt;=1,ISNUMBER(J148),J148&gt;=0,J148&lt;=1),D148/E148*1000,NA())</x:f>
+        <x:v>1.4680064000000002</x:v>
+      </x:c>
+      <x:c r="H148" s="33" t="n">
+        <x:f>G148+I148</x:f>
+        <x:v>1.6311182222222225</x:v>
+      </x:c>
+      <x:c r="I148" s="33" t="n">
+        <x:f>G148*F148*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0.16311182222222223</x:v>
+      </x:c>
+      <x:c r="J148" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K148" s="33" t="n">
+        <x:f>I148*J148</x:f>
+        <x:v>0.16311182222222223</x:v>
+      </x:c>
+      <x:c r="L148" s="29" t="str">
+        <x:v>原通信行 125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="23" customHeight="1">
+      <x:c r="A149" s="29" t="str">
+        <x:v>EP 期望</x:v>
+      </x:c>
+      <x:c r="B149" s="29" t="str">
+        <x:v>MoE Hidden</x:v>
+      </x:c>
+      <x:c r="C149" s="29" t="str">
+        <x:v>Dispatch 仅 Hidden</x:v>
+      </x:c>
+      <x:c r="D149" s="33" t="n">
+        <x:f>(K126*2^20)/1e9</x:f>
+        <x:v>4.8758784</x:v>
+      </x:c>
+      <x:c r="E149" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F149" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G149" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E149),E149&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F149),F149&gt;=0,F149&lt;=1,ISNUMBER(J149),J149&gt;=0,J149&lt;=1),D149/E149*1000,NA())</x:f>
+        <x:v>48.758784000000006</x:v>
+      </x:c>
+      <x:c r="H149" s="33" t="n">
+        <x:f>G149+I149</x:f>
+        <x:v>54.17642666666667</x:v>
+      </x:c>
+      <x:c r="I149" s="33" t="n">
+        <x:f>G149*F149*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>5.417642666666668</x:v>
+      </x:c>
+      <x:c r="J149" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K149" s="33" t="n">
+        <x:f>I149*J149</x:f>
+        <x:v>5.417642666666668</x:v>
+      </x:c>
+      <x:c r="L149" s="29" t="str">
+        <x:v>原通信行 126</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="23" customHeight="1">
+      <x:c r="A150" s="29" t="str">
+        <x:v>EP 期望</x:v>
+      </x:c>
+      <x:c r="B150" s="29" t="str">
+        <x:v>MoE Hidden</x:v>
+      </x:c>
+      <x:c r="C150" s="29" t="str">
+        <x:v>Combine 仅 Hidden</x:v>
+      </x:c>
+      <x:c r="D150" s="33" t="n">
+        <x:f>(K127*2^20)/1e9</x:f>
+        <x:v>4.8758784</x:v>
+      </x:c>
+      <x:c r="E150" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F150" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G150" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E150),E150&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F150),F150&gt;=0,F150&lt;=1,ISNUMBER(J150),J150&gt;=0,J150&lt;=1),D150/E150*1000,NA())</x:f>
+        <x:v>48.758784000000006</x:v>
+      </x:c>
+      <x:c r="H150" s="33" t="n">
+        <x:f>G150+I150</x:f>
+        <x:v>54.17642666666667</x:v>
+      </x:c>
+      <x:c r="I150" s="33" t="n">
+        <x:f>G150*F150*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>5.417642666666668</x:v>
+      </x:c>
+      <x:c r="J150" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K150" s="33" t="n">
+        <x:f>I150*J150</x:f>
+        <x:v>5.417642666666668</x:v>
+      </x:c>
+      <x:c r="L150" s="29" t="str">
+        <x:v>原通信行 127</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="23" customHeight="1">
+      <x:c r="A151" s="29" t="str">
+        <x:v>Engram</x:v>
+      </x:c>
+      <x:c r="B151" s="29" t="str">
+        <x:v>Node Metadata</x:v>
+      </x:c>
+      <x:c r="C151" s="29" t="str">
+        <x:v>两表合并 Counts</x:v>
+      </x:c>
+      <x:c r="D151" s="33" t="n">
+        <x:f>(K128*2^20)/1e9</x:f>
+        <x:v>0.000001008</x:v>
+      </x:c>
+      <x:c r="E151" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F151" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G151" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E151),E151&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F151),F151&gt;=0,F151&lt;=1,ISNUMBER(J151),J151&gt;=0,J151&lt;=1),D151/E151*1000,NA())</x:f>
+        <x:v>0.00001008</x:v>
+      </x:c>
+      <x:c r="H151" s="33" t="n">
+        <x:f>G151+I151</x:f>
+        <x:v>0.0000112</x:v>
+      </x:c>
+      <x:c r="I151" s="33" t="n">
+        <x:f>G151*F151*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0.00000112</x:v>
+      </x:c>
+      <x:c r="J151" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K151" s="33" t="n">
+        <x:f>I151*J151</x:f>
+        <x:v>0.00000112</x:v>
+      </x:c>
+      <x:c r="L151" s="29" t="str">
+        <x:v>原通信行 128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="23" customHeight="1">
+      <x:c r="A152" s="29" t="str">
+        <x:v>Engram 期望</x:v>
+      </x:c>
+      <x:c r="B152" s="29" t="str">
+        <x:v>Node IDs</x:v>
+      </x:c>
+      <x:c r="C152" s="29" t="str">
+        <x:v>均匀 Owner 路由</x:v>
+      </x:c>
+      <x:c r="D152" s="33" t="n">
+        <x:f>(K129*2^20)/1e9</x:f>
+        <x:v>0.000688128</x:v>
+      </x:c>
+      <x:c r="E152" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F152" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G152" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E152),E152&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F152),F152&gt;=0,F152&lt;=1,ISNUMBER(J152),J152&gt;=0,J152&lt;=1),D152/E152*1000,NA())</x:f>
+        <x:v>0.00688128</x:v>
+      </x:c>
+      <x:c r="H152" s="33" t="n">
+        <x:f>G152+I152</x:f>
+        <x:v>0.007645866666666667</x:v>
+      </x:c>
+      <x:c r="I152" s="33" t="n">
+        <x:f>G152*F152*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0.0007645866666666668</x:v>
+      </x:c>
+      <x:c r="J152" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K152" s="33" t="n">
+        <x:f>I152*J152</x:f>
+        <x:v>0.0007645866666666668</x:v>
+      </x:c>
+      <x:c r="L152" s="29" t="str">
+        <x:v>原通信行 129</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="23" customHeight="1">
+      <x:c r="A153" s="29" t="str">
+        <x:v>Engram 期望</x:v>
+      </x:c>
+      <x:c r="B153" s="29" t="str">
+        <x:v>Node Responses</x:v>
+      </x:c>
+      <x:c r="C153" s="29" t="str">
+        <x:v>反向 BF16 返回</x:v>
+      </x:c>
+      <x:c r="D153" s="33" t="n">
+        <x:f>(K130*2^20)/1e9</x:f>
+        <x:v>0.044040192</x:v>
+      </x:c>
+      <x:c r="E153" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F153" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G153" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E153),E153&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F153),F153&gt;=0,F153&lt;=1,ISNUMBER(J153),J153&gt;=0,J153&lt;=1),D153/E153*1000,NA())</x:f>
+        <x:v>0.44040192</x:v>
+      </x:c>
+      <x:c r="H153" s="33" t="n">
+        <x:f>G153+I153</x:f>
+        <x:v>0.48933546666666666</x:v>
+      </x:c>
+      <x:c r="I153" s="33" t="n">
+        <x:f>G153*F153*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0.048933546666666675</x:v>
+      </x:c>
+      <x:c r="J153" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K153" s="33" t="n">
+        <x:f>I153*J153</x:f>
+        <x:v>0.048933546666666675</x:v>
+      </x:c>
+      <x:c r="L153" s="29" t="str">
+        <x:v>原通信行 130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="23" customHeight="1">
+      <x:c r="A154" s="29" t="str">
+        <x:v>Engram</x:v>
+      </x:c>
+      <x:c r="B154" s="29" t="str">
+        <x:v>TP Lookup</x:v>
+      </x:c>
+      <x:c r="C154" s="29" t="str">
+        <x:v>两表合并广播</x:v>
+      </x:c>
+      <x:c r="D154" s="33" t="n">
+        <x:f>(K131*2^20)/1e9</x:f>
+        <x:v>0.352321536</x:v>
+      </x:c>
+      <x:c r="E154" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F154" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G154" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E154),E154&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F154),F154&gt;=0,F154&lt;=1,ISNUMBER(J154),J154&gt;=0,J154&lt;=1),D154/E154*1000,NA())</x:f>
+        <x:v>3.52321536</x:v>
+      </x:c>
+      <x:c r="H154" s="33" t="n">
+        <x:f>G154+I154</x:f>
+        <x:v>3.9146837333333333</x:v>
+      </x:c>
+      <x:c r="I154" s="33" t="n">
+        <x:f>G154*F154*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0.3914683733333334</x:v>
+      </x:c>
+      <x:c r="J154" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K154" s="33" t="n">
+        <x:f>I154*J154</x:f>
+        <x:v>0.3914683733333334</x:v>
+      </x:c>
+      <x:c r="L154" s="29" t="str">
+        <x:v>原通信行 131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="23" customHeight="1">
+      <x:c r="A155" s="29" t="str">
+        <x:v>EP</x:v>
+      </x:c>
+      <x:c r="B155" s="29" t="str">
+        <x:v>MoE 计数</x:v>
+      </x:c>
+      <x:c r="C155" s="29" t="str">
+        <x:v>直方图 Ring AG</x:v>
+      </x:c>
+      <x:c r="D155" s="33" t="n">
+        <x:f>(IF(E126=0,0,H126*ROUNDUP(384/G126,0)*G126*4*(G126-1)))/1e9</x:f>
+        <x:v>0.00190464</x:v>
+      </x:c>
+      <x:c r="E155" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F155" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G155" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E155),E155&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F155),F155&gt;=0,F155&lt;=1,ISNUMBER(J155),J155&gt;=0,J155&lt;=1),D155/E155*1000,NA())</x:f>
+        <x:v>0.0190464</x:v>
+      </x:c>
+      <x:c r="H155" s="33" t="n">
+        <x:f>G155+I155</x:f>
+        <x:v>0.02116266666666667</x:v>
+      </x:c>
+      <x:c r="I155" s="33" t="n">
+        <x:f>G155*F155*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0.0021162666666666666</x:v>
+      </x:c>
+      <x:c r="J155" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K155" s="33" t="n">
+        <x:f>I155*J155</x:f>
+        <x:v>0.0021162666666666666</x:v>
+      </x:c>
+      <x:c r="L155" s="29" t="str">
+        <x:v>额外控制量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="23" customHeight="1">
+      <x:c r="A156" s="57" t="str">
+        <x:v>所列事件串行相加</x:v>
+      </x:c>
+      <x:c r="B156" s="57"/>
+      <x:c r="C156" s="57"/>
+      <x:c r="D156" s="58" t="n">
+        <x:f>SUM(D144:D155)</x:f>
+        <x:v>26.739184624000004</x:v>
+      </x:c>
+      <x:c r="E156" s="58"/>
+      <x:c r="F156" s="57"/>
+      <x:c r="G156" s="58" t="n">
+        <x:f>SUM(G144:G155)</x:f>
+        <x:v>267.39184624</x:v>
+      </x:c>
+      <x:c r="H156" s="58" t="n">
+        <x:f>SUM(H144:H155)</x:f>
+        <x:v>297.1020513777778</x:v>
+      </x:c>
+      <x:c r="I156" s="58" t="n">
+        <x:f>SUM(I144:I155)</x:f>
+        <x:v>29.710205137777784</x:v>
+      </x:c>
+      <x:c r="J156" s="57"/>
+      <x:c r="K156" s="58" t="n">
+        <x:f>SUM(K144:K155)</x:f>
+        <x:v>29.710205137777784</x:v>
+      </x:c>
+      <x:c r="L156" s="57"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="O56:P56"/>
@@ -6249,6 +7114,9 @@
     <x:mergeCell ref="O63:P63"/>
     <x:mergeCell ref="O64:P64"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="L140:L140">
+    <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="不一致"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -12101,6 +12969,785 @@
       <x:c r="O132" s="29"/>
       <x:c r="P132" s="29"/>
     </x:row>
+    <x:row r="135" ht="23" customHeight="1">
+      <x:c r="A135" s="46" t="str">
+        <x:v>PD 带宽争用耗时评估</x:v>
+      </x:c>
+      <x:c r="B135" s="29"/>
+      <x:c r="C135" s="29"/>
+      <x:c r="D135" s="29"/>
+      <x:c r="E135" s="29"/>
+      <x:c r="F135" s="29"/>
+      <x:c r="G135" s="29"/>
+      <x:c r="H135" s="29"/>
+      <x:c r="I135" s="29"/>
+      <x:c r="J135" s="29"/>
+      <x:c r="K135" s="29"/>
+      <x:c r="L135" s="29"/>
+    </x:row>
+    <x:row r="136" ht="23" customHeight="1">
+      <x:c r="A136" s="29" t="str">
+        <x:v>Decode 当前表参数；100 GB/s 为归一化示例。所列事件的带宽项，不等于完整 forward 耗时。</x:v>
+      </x:c>
+      <x:c r="B136" s="29"/>
+      <x:c r="C136" s="29"/>
+      <x:c r="D136" s="29"/>
+      <x:c r="E136" s="29"/>
+      <x:c r="F136" s="29"/>
+      <x:c r="G136" s="29"/>
+      <x:c r="H136" s="29"/>
+      <x:c r="I136" s="29"/>
+      <x:c r="J136" s="29"/>
+      <x:c r="K136" s="29"/>
+      <x:c r="L136" s="29"/>
+    </x:row>
+    <x:row r="137" ht="38" customHeight="1">
+      <x:c r="A137" s="49" t="str">
+        <x:v>带宽降幅</x:v>
+      </x:c>
+      <x:c r="B137" s="49" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="C137" s="49" t="str">
+        <x:v>争用覆盖率</x:v>
+      </x:c>
+      <x:c r="D137" s="49" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="E137" s="49" t="str">
+        <x:v>基线 forward ms</x:v>
+      </x:c>
+      <x:c r="F137" s="49" t="str">
+        <x:v>实测输入</x:v>
+      </x:c>
+      <x:c r="G137" s="49" t="str">
+        <x:v>默认带宽 GB/s</x:v>
+      </x:c>
+      <x:c r="H137" s="49" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="I137" s="29"/>
+      <x:c r="J137" s="29"/>
+      <x:c r="K137" s="29"/>
+      <x:c r="L137" s="29"/>
+    </x:row>
+    <x:row r="138" ht="23" customHeight="1">
+      <x:c r="A138" s="29"/>
+      <x:c r="B138" s="51" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="C138" s="29"/>
+      <x:c r="D138" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E138" s="29"/>
+      <x:c r="F138" s="52"/>
+      <x:c r="G138" s="29"/>
+      <x:c r="H138" s="52" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I138" s="29"/>
+      <x:c r="J138" s="29"/>
+      <x:c r="K138" s="29"/>
+      <x:c r="L138" s="29"/>
+    </x:row>
+    <x:row r="139" ht="38" customHeight="1">
+      <x:c r="A139" s="49" t="str">
+        <x:v>通信基线 ms</x:v>
+      </x:c>
+      <x:c r="B139" s="49" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="C139" s="49" t="str">
+        <x:v>通信争用后 ms</x:v>
+      </x:c>
+      <x:c r="D139" s="49" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="E139" s="49" t="str">
+        <x:v>forward 增量 ms</x:v>
+      </x:c>
+      <x:c r="F139" s="49" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="G139" s="49" t="str">
+        <x:v>forward 新耗时 ms</x:v>
+      </x:c>
+      <x:c r="H139" s="49" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="I139" s="49" t="str">
+        <x:v>forward 增幅</x:v>
+      </x:c>
+      <x:c r="J139" s="49" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="K139" s="49" t="str">
+        <x:v>输入状态</x:v>
+      </x:c>
+      <x:c r="L139" s="49" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="23" customHeight="1">
+      <x:c r="A140" s="53"/>
+      <x:c r="B140" s="53" t="n">
+        <x:f>SUM(G144:G155)</x:f>
+        <x:v>6.44184048</x:v>
+      </x:c>
+      <x:c r="C140" s="53"/>
+      <x:c r="D140" s="53" t="n">
+        <x:f>SUM(H144:H155)</x:f>
+        <x:v>7.157600533333333</x:v>
+      </x:c>
+      <x:c r="E140" s="53"/>
+      <x:c r="F140" s="53" t="n">
+        <x:f>SUM(K144:K155)</x:f>
+        <x:v>0.7157600533333335</x:v>
+      </x:c>
+      <x:c r="G140" s="53"/>
+      <x:c r="H140" s="53" t="str">
+        <x:f>IF(AND(ISNUMBER($F$138),$F$138&gt;0,$F$138&gt;=SUMPRODUCT(G144:G155,J144:J155)),$F$138+F140,"")</x:f>
+      </x:c>
+      <x:c r="I140" s="53"/>
+      <x:c r="J140" s="54" t="str">
+        <x:f>IF(AND(ISNUMBER($F$138),$F$138&gt;0,$F$138&gt;=SUMPRODUCT(G144:G155,J144:J155)),F140/$F$138,"")</x:f>
+      </x:c>
+      <x:c r="K140" s="53"/>
+      <x:c r="L140" s="53" t="str">
+        <x:f>IF($F$138="","待填基线",IF(AND(ISNUMBER($F$138),$F$138&gt;0,$F$138&gt;=SUMPRODUCT(G144:G155,J144:J155)),"已填基线","基线/暴露不一致"))</x:f>
+        <x:v>待填基线</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" ht="23" customHeight="1">
+      <x:c r="A141" s="29" t="str">
+        <x:v>共享比例=0 表示独立链路；暴露系数=0 表示增量完全隐藏。默认均为 1，降幅只作用于带宽项。</x:v>
+      </x:c>
+      <x:c r="B141" s="29"/>
+      <x:c r="C141" s="29"/>
+      <x:c r="D141" s="29"/>
+      <x:c r="E141" s="29"/>
+      <x:c r="F141" s="29"/>
+      <x:c r="G141" s="29"/>
+      <x:c r="H141" s="29"/>
+      <x:c r="I141" s="29"/>
+      <x:c r="J141" s="29"/>
+      <x:c r="K141" s="29"/>
+      <x:c r="L141" s="29"/>
+    </x:row>
+    <x:row r="142" ht="23" customHeight="1">
+      <x:c r="A142" s="29" t="str">
+        <x:v>V4.1 为 PD 条件评估；旧 KV 规划与新 main 的端到端迁移可用性未在本次验证。</x:v>
+      </x:c>
+      <x:c r="B142" s="29"/>
+      <x:c r="C142" s="29"/>
+      <x:c r="D142" s="29"/>
+      <x:c r="E142" s="29"/>
+      <x:c r="F142" s="29"/>
+      <x:c r="G142" s="29"/>
+      <x:c r="H142" s="29"/>
+      <x:c r="I142" s="29"/>
+      <x:c r="J142" s="29"/>
+      <x:c r="K142" s="29"/>
+      <x:c r="L142" s="29"/>
+    </x:row>
+    <x:row r="143" ht="38" customHeight="1">
+      <x:c r="A143" s="49" t="str">
+        <x:v>并行域</x:v>
+      </x:c>
+      <x:c r="B143" s="49" t="str">
+        <x:v>模块</x:v>
+      </x:c>
+      <x:c r="C143" s="49" t="str">
+        <x:v>通信事件</x:v>
+      </x:c>
+      <x:c r="D143" s="49" t="str">
+        <x:v>GB/Rank/Step</x:v>
+      </x:c>
+      <x:c r="E143" s="49" t="str">
+        <x:v>有效带宽 GB/s</x:v>
+      </x:c>
+      <x:c r="F143" s="49" t="str">
+        <x:v>共享比例</x:v>
+      </x:c>
+      <x:c r="G143" s="49" t="str">
+        <x:v>基线带宽项 ms</x:v>
+      </x:c>
+      <x:c r="H143" s="49" t="str">
+        <x:v>争用后带宽项 ms</x:v>
+      </x:c>
+      <x:c r="I143" s="49" t="str">
+        <x:v>通信增量 ms</x:v>
+      </x:c>
+      <x:c r="J143" s="49" t="str">
+        <x:v>暴露系数</x:v>
+      </x:c>
+      <x:c r="K143" s="49" t="str">
+        <x:v>forward 增量 ms</x:v>
+      </x:c>
+      <x:c r="L143" s="49" t="str">
+        <x:v>公式口径</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" ht="23" customHeight="1">
+      <x:c r="A144" s="29" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B144" s="29" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C144" s="29" t="str">
+        <x:v>逐层输入</x:v>
+      </x:c>
+      <x:c r="D144" s="33" t="n">
+        <x:f>(K121*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E144" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F144" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G144" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E144),E144&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F144),F144&gt;=0,F144&lt;=1,ISNUMBER(J144),J144&gt;=0,J144&lt;=1),D144/E144*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H144" s="33" t="n">
+        <x:f>G144+I144</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I144" s="33" t="n">
+        <x:f>G144*F144*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J144" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K144" s="33" t="n">
+        <x:f>I144*J144</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L144" s="29" t="str">
+        <x:v>原通信行 121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="23" customHeight="1">
+      <x:c r="A145" s="29" t="str">
+        <x:v>DSA CP</x:v>
+      </x:c>
+      <x:c r="B145" s="29" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C145" s="29" t="str">
+        <x:v>Token/Head 交换</x:v>
+      </x:c>
+      <x:c r="D145" s="33" t="n">
+        <x:f>(K122*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E145" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F145" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G145" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E145),E145&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F145),F145&gt;=0,F145&lt;=1,ISNUMBER(J145),J145&gt;=0,J145&lt;=1),D145/E145*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H145" s="33" t="n">
+        <x:f>G145+I145</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I145" s="33" t="n">
+        <x:f>G145*F145*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J145" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K145" s="33" t="n">
+        <x:f>I145*J145</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L145" s="29" t="str">
+        <x:v>原通信行 122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="23" customHeight="1">
+      <x:c r="A146" s="29" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B146" s="29" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C146" s="29" t="str">
+        <x:v>O Proj 后</x:v>
+      </x:c>
+      <x:c r="D146" s="33" t="n">
+        <x:f>(K123*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E146" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F146" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G146" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E146),E146&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F146),F146&gt;=0,F146&lt;=1,ISNUMBER(J146),J146&gt;=0,J146&lt;=1),D146/E146*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H146" s="33" t="n">
+        <x:f>G146+I146</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I146" s="33" t="n">
+        <x:f>G146*F146*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J146" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K146" s="33" t="n">
+        <x:f>I146*J146</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L146" s="29" t="str">
+        <x:v>原通信行 123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="23" customHeight="1">
+      <x:c r="A147" s="29" t="str">
+        <x:v>Attention TP</x:v>
+      </x:c>
+      <x:c r="B147" s="29" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C147" s="29" t="str">
+        <x:v>非 SP 输出</x:v>
+      </x:c>
+      <x:c r="D147" s="33" t="n">
+        <x:f>(K124*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E147" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F147" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G147" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E147),E147&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F147),F147&gt;=0,F147&lt;=1,ISNUMBER(J147),J147&gt;=0,J147&lt;=1),D147/E147*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H147" s="33" t="n">
+        <x:f>G147+I147</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I147" s="33" t="n">
+        <x:f>G147*F147*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J147" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K147" s="33" t="n">
+        <x:f>I147*J147</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L147" s="29" t="str">
+        <x:v>原通信行 124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="23" customHeight="1">
+      <x:c r="A148" s="29" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B148" s="29" t="str">
+        <x:v>Model Output</x:v>
+      </x:c>
+      <x:c r="C148" s="29" t="str">
+        <x:v>最终 Hidden</x:v>
+      </x:c>
+      <x:c r="D148" s="33" t="n">
+        <x:f>(K125*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E148" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F148" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G148" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E148),E148&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F148),F148&gt;=0,F148&lt;=1,ISNUMBER(J148),J148&gt;=0,J148&lt;=1),D148/E148*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H148" s="33" t="n">
+        <x:f>G148+I148</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I148" s="33" t="n">
+        <x:f>G148*F148*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J148" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K148" s="33" t="n">
+        <x:f>I148*J148</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L148" s="29" t="str">
+        <x:v>原通信行 125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="23" customHeight="1">
+      <x:c r="A149" s="29" t="str">
+        <x:v>EP 期望</x:v>
+      </x:c>
+      <x:c r="B149" s="29" t="str">
+        <x:v>MoE Hidden</x:v>
+      </x:c>
+      <x:c r="C149" s="29" t="str">
+        <x:v>MC2 FullMesh Dispatch</x:v>
+      </x:c>
+      <x:c r="D149" s="33" t="n">
+        <x:f>(IF(F126=2,E126/5120*H126*(ROUNDUP((ROUNDUP(5120*F126/32,0)*32+32)/480,0)*512),NA()))/1e9</x:f>
+        <x:v>0.33521664</x:v>
+      </x:c>
+      <x:c r="E149" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F149" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G149" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E149),E149&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F149),F149&gt;=0,F149&lt;=1,ISNUMBER(J149),J149&gt;=0,J149&lt;=1),D149/E149*1000,NA())</x:f>
+        <x:v>3.3521664</x:v>
+      </x:c>
+      <x:c r="H149" s="33" t="n">
+        <x:f>G149+I149</x:f>
+        <x:v>3.7246293333333336</x:v>
+      </x:c>
+      <x:c r="I149" s="33" t="n">
+        <x:f>G149*F149*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0.3724629333333334</x:v>
+      </x:c>
+      <x:c r="J149" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K149" s="33" t="n">
+        <x:f>I149*J149</x:f>
+        <x:v>0.3724629333333334</x:v>
+      </x:c>
+      <x:c r="L149" s="29" t="str">
+        <x:v>原通信行 126</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="23" customHeight="1">
+      <x:c r="A150" s="29" t="str">
+        <x:v>EP 期望</x:v>
+      </x:c>
+      <x:c r="B150" s="29" t="str">
+        <x:v>MoE Hidden</x:v>
+      </x:c>
+      <x:c r="C150" s="29" t="str">
+        <x:v>MC2 Combine + flags</x:v>
+      </x:c>
+      <x:c r="D150" s="33" t="n">
+        <x:f>(IF(F127=2,K127*2^20+E127/5120*H127*32,NA()))/1e9</x:f>
+        <x:v>0.30569472</x:v>
+      </x:c>
+      <x:c r="E150" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F150" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G150" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E150),E150&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F150),F150&gt;=0,F150&lt;=1,ISNUMBER(J150),J150&gt;=0,J150&lt;=1),D150/E150*1000,NA())</x:f>
+        <x:v>3.0569471999999998</x:v>
+      </x:c>
+      <x:c r="H150" s="33" t="n">
+        <x:f>G150+I150</x:f>
+        <x:v>3.3966079999999996</x:v>
+      </x:c>
+      <x:c r="I150" s="33" t="n">
+        <x:f>G150*F150*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0.3396608</x:v>
+      </x:c>
+      <x:c r="J150" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K150" s="33" t="n">
+        <x:f>I150*J150</x:f>
+        <x:v>0.3396608</x:v>
+      </x:c>
+      <x:c r="L150" s="29" t="str">
+        <x:v>原通信行 127</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="23" customHeight="1">
+      <x:c r="A151" s="29" t="str">
+        <x:v>Engram</x:v>
+      </x:c>
+      <x:c r="B151" s="29" t="str">
+        <x:v>Node Metadata</x:v>
+      </x:c>
+      <x:c r="C151" s="29" t="str">
+        <x:v>两表合并 Counts</x:v>
+      </x:c>
+      <x:c r="D151" s="33" t="n">
+        <x:f>(K128*2^20)/1e9</x:f>
+        <x:v>0.000001008</x:v>
+      </x:c>
+      <x:c r="E151" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F151" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G151" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E151),E151&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F151),F151&gt;=0,F151&lt;=1,ISNUMBER(J151),J151&gt;=0,J151&lt;=1),D151/E151*1000,NA())</x:f>
+        <x:v>0.00001008</x:v>
+      </x:c>
+      <x:c r="H151" s="33" t="n">
+        <x:f>G151+I151</x:f>
+        <x:v>0.0000112</x:v>
+      </x:c>
+      <x:c r="I151" s="33" t="n">
+        <x:f>G151*F151*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0.00000112</x:v>
+      </x:c>
+      <x:c r="J151" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K151" s="33" t="n">
+        <x:f>I151*J151</x:f>
+        <x:v>0.00000112</x:v>
+      </x:c>
+      <x:c r="L151" s="29" t="str">
+        <x:v>原通信行 128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="23" customHeight="1">
+      <x:c r="A152" s="29" t="str">
+        <x:v>Engram 期望</x:v>
+      </x:c>
+      <x:c r="B152" s="29" t="str">
+        <x:v>Node IDs</x:v>
+      </x:c>
+      <x:c r="C152" s="29" t="str">
+        <x:v>均匀 Owner 路由</x:v>
+      </x:c>
+      <x:c r="D152" s="33" t="n">
+        <x:f>(K129*2^20)/1e9</x:f>
+        <x:v>0.000043008</x:v>
+      </x:c>
+      <x:c r="E152" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F152" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G152" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E152),E152&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F152),F152&gt;=0,F152&lt;=1,ISNUMBER(J152),J152&gt;=0,J152&lt;=1),D152/E152*1000,NA())</x:f>
+        <x:v>0.00043008</x:v>
+      </x:c>
+      <x:c r="H152" s="33" t="n">
+        <x:f>G152+I152</x:f>
+        <x:v>0.00047786666666666666</x:v>
+      </x:c>
+      <x:c r="I152" s="33" t="n">
+        <x:f>G152*F152*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0.000047786666666666674</x:v>
+      </x:c>
+      <x:c r="J152" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K152" s="33" t="n">
+        <x:f>I152*J152</x:f>
+        <x:v>0.000047786666666666674</x:v>
+      </x:c>
+      <x:c r="L152" s="29" t="str">
+        <x:v>原通信行 129</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="23" customHeight="1">
+      <x:c r="A153" s="29" t="str">
+        <x:v>Engram 期望</x:v>
+      </x:c>
+      <x:c r="B153" s="29" t="str">
+        <x:v>Node Responses</x:v>
+      </x:c>
+      <x:c r="C153" s="29" t="str">
+        <x:v>反向 BF16 返回</x:v>
+      </x:c>
+      <x:c r="D153" s="33" t="n">
+        <x:f>(K130*2^20)/1e9</x:f>
+        <x:v>0.002752512</x:v>
+      </x:c>
+      <x:c r="E153" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F153" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G153" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E153),E153&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F153),F153&gt;=0,F153&lt;=1,ISNUMBER(J153),J153&gt;=0,J153&lt;=1),D153/E153*1000,NA())</x:f>
+        <x:v>0.02752512</x:v>
+      </x:c>
+      <x:c r="H153" s="33" t="n">
+        <x:f>G153+I153</x:f>
+        <x:v>0.030583466666666666</x:v>
+      </x:c>
+      <x:c r="I153" s="33" t="n">
+        <x:f>G153*F153*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0.003058346666666667</x:v>
+      </x:c>
+      <x:c r="J153" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K153" s="33" t="n">
+        <x:f>I153*J153</x:f>
+        <x:v>0.003058346666666667</x:v>
+      </x:c>
+      <x:c r="L153" s="29" t="str">
+        <x:v>原通信行 130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="23" customHeight="1">
+      <x:c r="A154" s="29" t="str">
+        <x:v>Engram</x:v>
+      </x:c>
+      <x:c r="B154" s="29" t="str">
+        <x:v>TP Lookup</x:v>
+      </x:c>
+      <x:c r="C154" s="29" t="str">
+        <x:v>两表合并广播</x:v>
+      </x:c>
+      <x:c r="D154" s="33" t="n">
+        <x:f>(K131*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E154" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F154" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G154" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E154),E154&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F154),F154&gt;=0,F154&lt;=1,ISNUMBER(J154),J154&gt;=0,J154&lt;=1),D154/E154*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H154" s="33" t="n">
+        <x:f>G154+I154</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I154" s="33" t="n">
+        <x:f>G154*F154*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J154" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K154" s="33" t="n">
+        <x:f>I154*J154</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L154" s="29" t="str">
+        <x:v>原通信行 131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="23" customHeight="1">
+      <x:c r="A155" s="29" t="str">
+        <x:v>EP</x:v>
+      </x:c>
+      <x:c r="B155" s="29" t="str">
+        <x:v>MoE 计数</x:v>
+      </x:c>
+      <x:c r="C155" s="29" t="str">
+        <x:v>MC2 count 写入</x:v>
+      </x:c>
+      <x:c r="D155" s="33" t="n">
+        <x:f>(IF(E126=0,0,H126*ROUNDUP(384/G126,0)*(G126-1)*32))/1e9</x:f>
+        <x:v>0.00047616</x:v>
+      </x:c>
+      <x:c r="E155" s="55" t="n">
+        <x:f>$H$138</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F155" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G155" s="33" t="n">
+        <x:f>IF(AND(ISNUMBER(E155),E155&gt;0,ISNUMBER($B$138),$B$138&gt;=0,$B$138&lt;1,ISNUMBER($D$138),$D$138&gt;=0,$D$138&lt;=1,ISNUMBER(F155),F155&gt;=0,F155&lt;=1,ISNUMBER(J155),J155&gt;=0,J155&lt;=1),D155/E155*1000,NA())</x:f>
+        <x:v>0.0047616</x:v>
+      </x:c>
+      <x:c r="H155" s="33" t="n">
+        <x:f>G155+I155</x:f>
+        <x:v>0.0052906666666666675</x:v>
+      </x:c>
+      <x:c r="I155" s="33" t="n">
+        <x:f>G155*F155*$D$138*$B$138/(1-$B$138)</x:f>
+        <x:v>0.0005290666666666667</x:v>
+      </x:c>
+      <x:c r="J155" s="56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K155" s="33" t="n">
+        <x:f>I155*J155</x:f>
+        <x:v>0.0005290666666666667</x:v>
+      </x:c>
+      <x:c r="L155" s="29" t="str">
+        <x:v>额外控制量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="23" customHeight="1">
+      <x:c r="A156" s="57" t="str">
+        <x:v>所列事件串行相加</x:v>
+      </x:c>
+      <x:c r="B156" s="57"/>
+      <x:c r="C156" s="57"/>
+      <x:c r="D156" s="58" t="n">
+        <x:f>SUM(D144:D155)</x:f>
+        <x:v>0.6441840480000001</x:v>
+      </x:c>
+      <x:c r="E156" s="58"/>
+      <x:c r="F156" s="57"/>
+      <x:c r="G156" s="58" t="n">
+        <x:f>SUM(G144:G155)</x:f>
+        <x:v>6.44184048</x:v>
+      </x:c>
+      <x:c r="H156" s="58" t="n">
+        <x:f>SUM(H144:H155)</x:f>
+        <x:v>7.157600533333333</x:v>
+      </x:c>
+      <x:c r="I156" s="58" t="n">
+        <x:f>SUM(I144:I155)</x:f>
+        <x:v>0.7157600533333335</x:v>
+      </x:c>
+      <x:c r="J156" s="57"/>
+      <x:c r="K156" s="58" t="n">
+        <x:f>SUM(K144:K155)</x:f>
+        <x:v>0.7157600533333335</x:v>
+      </x:c>
+      <x:c r="L156" s="57"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="O56:P56"/>
@@ -12113,6 +13760,9 @@
     <x:mergeCell ref="O63:P63"/>
     <x:mergeCell ref="O64:P64"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="L140:L140">
+    <x:cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="不一致"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/models/deepseek-v4.1-flash/deepseek-v4.1-flash-analysis.xlsx
+++ b/models/deepseek-v4.1-flash/deepseek-v4.1-flash-analysis.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R1d9b7ffae8a34ab1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="R212b10e90e21422f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R5514dda397fa4d82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="Rce1c059880a440c4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -57,7 +57,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -92,6 +92,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE8EEF5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -129,7 +134,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="59">
+  <x:cellXfs count="70">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -255,6 +260,39 @@
     <x:xf numFmtId="203" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -265,7 +303,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -275,7 +313,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -6323,8 +6361,8 @@
       <x:c r="O132" s="29"/>
       <x:c r="P132" s="29"/>
     </x:row>
-    <x:row r="135" ht="23" customHeight="1">
-      <x:c r="A135" s="46" t="str">
+    <x:row r="135" ht="15" customHeight="1">
+      <x:c r="A135" s="38" t="str">
         <x:v>PD 带宽争用耗时评估</x:v>
       </x:c>
       <x:c r="B135" s="29"/>
@@ -6339,7 +6377,7 @@
       <x:c r="K135" s="29"/>
       <x:c r="L135" s="29"/>
     </x:row>
-    <x:row r="136" ht="23" customHeight="1">
+    <x:row r="136" ht="15" customHeight="1">
       <x:c r="A136" s="29" t="str">
         <x:v>Prefill 当前表参数；100 GB/s 为归一化示例。所列事件的带宽项，不等于完整 forward 耗时。</x:v>
       </x:c>
@@ -6355,29 +6393,29 @@
       <x:c r="K136" s="29"/>
       <x:c r="L136" s="29"/>
     </x:row>
-    <x:row r="137" ht="38" customHeight="1">
-      <x:c r="A137" s="49" t="str">
+    <x:row r="137" ht="30" customHeight="1">
+      <x:c r="A137" s="66" t="str">
         <x:v>带宽降幅</x:v>
       </x:c>
-      <x:c r="B137" s="49" t="str">
+      <x:c r="B137" s="66" t="str">
         <x:v>输入</x:v>
       </x:c>
-      <x:c r="C137" s="49" t="str">
+      <x:c r="C137" s="66" t="str">
         <x:v>争用覆盖率</x:v>
       </x:c>
-      <x:c r="D137" s="49" t="str">
+      <x:c r="D137" s="66" t="str">
         <x:v>输入</x:v>
       </x:c>
-      <x:c r="E137" s="49" t="str">
+      <x:c r="E137" s="66" t="str">
         <x:v>基线 forward ms</x:v>
       </x:c>
-      <x:c r="F137" s="49" t="str">
+      <x:c r="F137" s="66" t="str">
         <x:v>实测输入</x:v>
       </x:c>
-      <x:c r="G137" s="49" t="str">
+      <x:c r="G137" s="66" t="str">
         <x:v>默认带宽 GB/s</x:v>
       </x:c>
-      <x:c r="H137" s="49" t="str">
+      <x:c r="H137" s="66" t="str">
         <x:v>输入</x:v>
       </x:c>
       <x:c r="I137" s="29"/>
@@ -6385,19 +6423,19 @@
       <x:c r="K137" s="29"/>
       <x:c r="L137" s="29"/>
     </x:row>
-    <x:row r="138" ht="23" customHeight="1">
+    <x:row r="138" ht="15" customHeight="1">
       <x:c r="A138" s="29"/>
-      <x:c r="B138" s="51" t="n">
+      <x:c r="B138" s="67" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C138" s="29"/>
-      <x:c r="D138" s="51" t="n">
+      <x:c r="D138" s="67" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E138" s="29"/>
-      <x:c r="F138" s="52"/>
+      <x:c r="F138" s="68"/>
       <x:c r="G138" s="29"/>
-      <x:c r="H138" s="52" t="n">
+      <x:c r="H138" s="35" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="I138" s="29"/>
@@ -6405,45 +6443,45 @@
       <x:c r="K138" s="29"/>
       <x:c r="L138" s="29"/>
     </x:row>
-    <x:row r="139" ht="38" customHeight="1">
-      <x:c r="A139" s="49" t="str">
+    <x:row r="139" ht="30" customHeight="1">
+      <x:c r="A139" s="66" t="str">
         <x:v>通信基线 ms</x:v>
       </x:c>
-      <x:c r="B139" s="49" t="str">
+      <x:c r="B139" s="66" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="C139" s="49" t="str">
+      <x:c r="C139" s="66" t="str">
         <x:v>通信争用后 ms</x:v>
       </x:c>
-      <x:c r="D139" s="49" t="str">
+      <x:c r="D139" s="66" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="E139" s="49" t="str">
+      <x:c r="E139" s="66" t="str">
         <x:v>forward 增量 ms</x:v>
       </x:c>
-      <x:c r="F139" s="49" t="str">
+      <x:c r="F139" s="66" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="G139" s="49" t="str">
+      <x:c r="G139" s="66" t="str">
         <x:v>forward 新耗时 ms</x:v>
       </x:c>
-      <x:c r="H139" s="49" t="str">
+      <x:c r="H139" s="66" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="I139" s="49" t="str">
+      <x:c r="I139" s="66" t="str">
         <x:v>forward 增幅</x:v>
       </x:c>
-      <x:c r="J139" s="49" t="str">
+      <x:c r="J139" s="66" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="K139" s="49" t="str">
+      <x:c r="K139" s="66" t="str">
         <x:v>输入状态</x:v>
       </x:c>
-      <x:c r="L139" s="49" t="str">
+      <x:c r="L139" s="66" t="str">
         <x:v>状态</x:v>
       </x:c>
     </x:row>
-    <x:row r="140" ht="23" customHeight="1">
+    <x:row r="140" ht="15" customHeight="1">
       <x:c r="A140" s="53"/>
       <x:c r="B140" s="53" t="n">
         <x:f>SUM(G144:G155)</x:f>
@@ -6473,7 +6511,7 @@
         <x:v>待填基线</x:v>
       </x:c>
     </x:row>
-    <x:row r="141" ht="23" customHeight="1">
+    <x:row r="141" ht="15" customHeight="1">
       <x:c r="A141" s="29" t="str">
         <x:v>共享比例=0 表示独立链路；暴露系数=0 表示增量完全隐藏。默认均为 1，降幅只作用于带宽项。</x:v>
       </x:c>
@@ -6489,7 +6527,7 @@
       <x:c r="K141" s="29"/>
       <x:c r="L141" s="29"/>
     </x:row>
-    <x:row r="142" ht="23" customHeight="1">
+    <x:row r="142" ht="15" customHeight="1">
       <x:c r="A142" s="29" t="str">
         <x:v>V4.1 为 PD 条件评估；旧 KV 规划与新 main 的端到端迁移可用性未在本次验证。</x:v>
       </x:c>
@@ -6505,45 +6543,45 @@
       <x:c r="K142" s="29"/>
       <x:c r="L142" s="29"/>
     </x:row>
-    <x:row r="143" ht="38" customHeight="1">
-      <x:c r="A143" s="49" t="str">
+    <x:row r="143" ht="30" customHeight="1">
+      <x:c r="A143" s="66" t="str">
         <x:v>并行域</x:v>
       </x:c>
-      <x:c r="B143" s="49" t="str">
+      <x:c r="B143" s="66" t="str">
         <x:v>模块</x:v>
       </x:c>
-      <x:c r="C143" s="49" t="str">
+      <x:c r="C143" s="66" t="str">
         <x:v>通信事件</x:v>
       </x:c>
-      <x:c r="D143" s="49" t="str">
+      <x:c r="D143" s="66" t="str">
         <x:v>GB/Rank/Step</x:v>
       </x:c>
-      <x:c r="E143" s="49" t="str">
+      <x:c r="E143" s="66" t="str">
         <x:v>有效带宽 GB/s</x:v>
       </x:c>
-      <x:c r="F143" s="49" t="str">
+      <x:c r="F143" s="66" t="str">
         <x:v>共享比例</x:v>
       </x:c>
-      <x:c r="G143" s="49" t="str">
+      <x:c r="G143" s="66" t="str">
         <x:v>基线带宽项 ms</x:v>
       </x:c>
-      <x:c r="H143" s="49" t="str">
+      <x:c r="H143" s="66" t="str">
         <x:v>争用后带宽项 ms</x:v>
       </x:c>
-      <x:c r="I143" s="49" t="str">
+      <x:c r="I143" s="66" t="str">
         <x:v>通信增量 ms</x:v>
       </x:c>
-      <x:c r="J143" s="49" t="str">
+      <x:c r="J143" s="66" t="str">
         <x:v>暴露系数</x:v>
       </x:c>
-      <x:c r="K143" s="49" t="str">
+      <x:c r="K143" s="66" t="str">
         <x:v>forward 增量 ms</x:v>
       </x:c>
-      <x:c r="L143" s="49" t="str">
+      <x:c r="L143" s="66" t="str">
         <x:v>公式口径</x:v>
       </x:c>
     </x:row>
-    <x:row r="144" ht="23" customHeight="1">
+    <x:row r="144" ht="15" customHeight="1">
       <x:c r="A144" s="29" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -6557,11 +6595,11 @@
         <x:f>(K121*2^20)/1e9</x:f>
         <x:v>5.8720256</x:v>
       </x:c>
-      <x:c r="E144" s="55" t="n">
+      <x:c r="E144" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F144" s="56" t="n">
+      <x:c r="F144" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G144" s="33" t="n">
@@ -6576,7 +6614,7 @@
         <x:f>G144*F144*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>6.524472888888889</x:v>
       </x:c>
-      <x:c r="J144" s="56" t="n">
+      <x:c r="J144" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K144" s="33" t="n">
@@ -6587,7 +6625,7 @@
         <x:v>原通信行 121</x:v>
       </x:c>
     </x:row>
-    <x:row r="145" ht="23" customHeight="1">
+    <x:row r="145" ht="15" customHeight="1">
       <x:c r="A145" s="29" t="str">
         <x:v>DSA CP</x:v>
       </x:c>
@@ -6601,11 +6639,11 @@
         <x:f>(K122*2^20)/1e9</x:f>
         <x:v>4.69762048</x:v>
       </x:c>
-      <x:c r="E145" s="55" t="n">
+      <x:c r="E145" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F145" s="56" t="n">
+      <x:c r="F145" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G145" s="33" t="n">
@@ -6620,7 +6658,7 @@
         <x:f>G145*F145*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>5.219578311111111</x:v>
       </x:c>
-      <x:c r="J145" s="56" t="n">
+      <x:c r="J145" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K145" s="33" t="n">
@@ -6631,7 +6669,7 @@
         <x:v>原通信行 122</x:v>
       </x:c>
     </x:row>
-    <x:row r="146" ht="23" customHeight="1">
+    <x:row r="146" ht="15" customHeight="1">
       <x:c r="A146" s="29" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -6645,11 +6683,11 @@
         <x:f>(K123*2^20)/1e9</x:f>
         <x:v>5.8720256</x:v>
       </x:c>
-      <x:c r="E146" s="55" t="n">
+      <x:c r="E146" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F146" s="56" t="n">
+      <x:c r="F146" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G146" s="33" t="n">
@@ -6664,7 +6702,7 @@
         <x:f>G146*F146*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>6.524472888888889</x:v>
       </x:c>
-      <x:c r="J146" s="56" t="n">
+      <x:c r="J146" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K146" s="33" t="n">
@@ -6675,7 +6713,7 @@
         <x:v>原通信行 123</x:v>
       </x:c>
     </x:row>
-    <x:row r="147" ht="23" customHeight="1">
+    <x:row r="147" ht="15" customHeight="1">
       <x:c r="A147" s="29" t="str">
         <x:v>Attention TP</x:v>
       </x:c>
@@ -6689,11 +6727,11 @@
         <x:f>(K124*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E147" s="55" t="n">
+      <x:c r="E147" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F147" s="56" t="n">
+      <x:c r="F147" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G147" s="33" t="n">
@@ -6708,7 +6746,7 @@
         <x:f>G147*F147*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J147" s="56" t="n">
+      <x:c r="J147" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K147" s="33" t="n">
@@ -6719,7 +6757,7 @@
         <x:v>原通信行 124</x:v>
       </x:c>
     </x:row>
-    <x:row r="148" ht="23" customHeight="1">
+    <x:row r="148" ht="15" customHeight="1">
       <x:c r="A148" s="29" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -6733,11 +6771,11 @@
         <x:f>(K125*2^20)/1e9</x:f>
         <x:v>0.14680064</x:v>
       </x:c>
-      <x:c r="E148" s="55" t="n">
+      <x:c r="E148" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F148" s="56" t="n">
+      <x:c r="F148" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G148" s="33" t="n">
@@ -6752,7 +6790,7 @@
         <x:f>G148*F148*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0.16311182222222223</x:v>
       </x:c>
-      <x:c r="J148" s="56" t="n">
+      <x:c r="J148" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K148" s="33" t="n">
@@ -6763,7 +6801,7 @@
         <x:v>原通信行 125</x:v>
       </x:c>
     </x:row>
-    <x:row r="149" ht="23" customHeight="1">
+    <x:row r="149" ht="15" customHeight="1">
       <x:c r="A149" s="29" t="str">
         <x:v>EP 期望</x:v>
       </x:c>
@@ -6777,11 +6815,11 @@
         <x:f>(K126*2^20)/1e9</x:f>
         <x:v>4.8758784</x:v>
       </x:c>
-      <x:c r="E149" s="55" t="n">
+      <x:c r="E149" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F149" s="56" t="n">
+      <x:c r="F149" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G149" s="33" t="n">
@@ -6796,7 +6834,7 @@
         <x:f>G149*F149*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>5.417642666666668</x:v>
       </x:c>
-      <x:c r="J149" s="56" t="n">
+      <x:c r="J149" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K149" s="33" t="n">
@@ -6807,7 +6845,7 @@
         <x:v>原通信行 126</x:v>
       </x:c>
     </x:row>
-    <x:row r="150" ht="23" customHeight="1">
+    <x:row r="150" ht="15" customHeight="1">
       <x:c r="A150" s="29" t="str">
         <x:v>EP 期望</x:v>
       </x:c>
@@ -6821,11 +6859,11 @@
         <x:f>(K127*2^20)/1e9</x:f>
         <x:v>4.8758784</x:v>
       </x:c>
-      <x:c r="E150" s="55" t="n">
+      <x:c r="E150" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F150" s="56" t="n">
+      <x:c r="F150" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G150" s="33" t="n">
@@ -6840,7 +6878,7 @@
         <x:f>G150*F150*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>5.417642666666668</x:v>
       </x:c>
-      <x:c r="J150" s="56" t="n">
+      <x:c r="J150" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K150" s="33" t="n">
@@ -6851,7 +6889,7 @@
         <x:v>原通信行 127</x:v>
       </x:c>
     </x:row>
-    <x:row r="151" ht="23" customHeight="1">
+    <x:row r="151" ht="15" customHeight="1">
       <x:c r="A151" s="29" t="str">
         <x:v>Engram</x:v>
       </x:c>
@@ -6865,11 +6903,11 @@
         <x:f>(K128*2^20)/1e9</x:f>
         <x:v>0.000001008</x:v>
       </x:c>
-      <x:c r="E151" s="55" t="n">
+      <x:c r="E151" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F151" s="56" t="n">
+      <x:c r="F151" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G151" s="33" t="n">
@@ -6884,7 +6922,7 @@
         <x:f>G151*F151*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0.00000112</x:v>
       </x:c>
-      <x:c r="J151" s="56" t="n">
+      <x:c r="J151" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K151" s="33" t="n">
@@ -6895,7 +6933,7 @@
         <x:v>原通信行 128</x:v>
       </x:c>
     </x:row>
-    <x:row r="152" ht="23" customHeight="1">
+    <x:row r="152" ht="15" customHeight="1">
       <x:c r="A152" s="29" t="str">
         <x:v>Engram 期望</x:v>
       </x:c>
@@ -6909,11 +6947,11 @@
         <x:f>(K129*2^20)/1e9</x:f>
         <x:v>0.000688128</x:v>
       </x:c>
-      <x:c r="E152" s="55" t="n">
+      <x:c r="E152" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F152" s="56" t="n">
+      <x:c r="F152" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G152" s="33" t="n">
@@ -6928,7 +6966,7 @@
         <x:f>G152*F152*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0.0007645866666666668</x:v>
       </x:c>
-      <x:c r="J152" s="56" t="n">
+      <x:c r="J152" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K152" s="33" t="n">
@@ -6939,7 +6977,7 @@
         <x:v>原通信行 129</x:v>
       </x:c>
     </x:row>
-    <x:row r="153" ht="23" customHeight="1">
+    <x:row r="153" ht="15" customHeight="1">
       <x:c r="A153" s="29" t="str">
         <x:v>Engram 期望</x:v>
       </x:c>
@@ -6953,11 +6991,11 @@
         <x:f>(K130*2^20)/1e9</x:f>
         <x:v>0.044040192</x:v>
       </x:c>
-      <x:c r="E153" s="55" t="n">
+      <x:c r="E153" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F153" s="56" t="n">
+      <x:c r="F153" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G153" s="33" t="n">
@@ -6972,7 +7010,7 @@
         <x:f>G153*F153*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0.048933546666666675</x:v>
       </x:c>
-      <x:c r="J153" s="56" t="n">
+      <x:c r="J153" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K153" s="33" t="n">
@@ -6983,7 +7021,7 @@
         <x:v>原通信行 130</x:v>
       </x:c>
     </x:row>
-    <x:row r="154" ht="23" customHeight="1">
+    <x:row r="154" ht="15" customHeight="1">
       <x:c r="A154" s="29" t="str">
         <x:v>Engram</x:v>
       </x:c>
@@ -6997,11 +7035,11 @@
         <x:f>(K131*2^20)/1e9</x:f>
         <x:v>0.352321536</x:v>
       </x:c>
-      <x:c r="E154" s="55" t="n">
+      <x:c r="E154" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F154" s="56" t="n">
+      <x:c r="F154" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G154" s="33" t="n">
@@ -7016,7 +7054,7 @@
         <x:f>G154*F154*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0.3914683733333334</x:v>
       </x:c>
-      <x:c r="J154" s="56" t="n">
+      <x:c r="J154" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K154" s="33" t="n">
@@ -7027,7 +7065,7 @@
         <x:v>原通信行 131</x:v>
       </x:c>
     </x:row>
-    <x:row r="155" ht="23" customHeight="1">
+    <x:row r="155" ht="15" customHeight="1">
       <x:c r="A155" s="29" t="str">
         <x:v>EP</x:v>
       </x:c>
@@ -7041,11 +7079,11 @@
         <x:f>(IF(E126=0,0,H126*ROUNDUP(384/G126,0)*G126*4*(G126-1)))/1e9</x:f>
         <x:v>0.00190464</x:v>
       </x:c>
-      <x:c r="E155" s="55" t="n">
+      <x:c r="E155" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F155" s="56" t="n">
+      <x:c r="F155" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G155" s="33" t="n">
@@ -7060,7 +7098,7 @@
         <x:f>G155*F155*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0.0021162666666666666</x:v>
       </x:c>
-      <x:c r="J155" s="56" t="n">
+      <x:c r="J155" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K155" s="33" t="n">
@@ -7071,36 +7109,36 @@
         <x:v>额外控制量</x:v>
       </x:c>
     </x:row>
-    <x:row r="156" ht="23" customHeight="1">
-      <x:c r="A156" s="57" t="str">
+    <x:row r="156" ht="15" customHeight="1">
+      <x:c r="A156" s="38" t="str">
         <x:v>所列事件串行相加</x:v>
       </x:c>
-      <x:c r="B156" s="57"/>
-      <x:c r="C156" s="57"/>
-      <x:c r="D156" s="58" t="n">
+      <x:c r="B156" s="38"/>
+      <x:c r="C156" s="38"/>
+      <x:c r="D156" s="39" t="n">
         <x:f>SUM(D144:D155)</x:f>
         <x:v>26.739184624000004</x:v>
       </x:c>
-      <x:c r="E156" s="58"/>
-      <x:c r="F156" s="57"/>
-      <x:c r="G156" s="58" t="n">
+      <x:c r="E156" s="38"/>
+      <x:c r="F156" s="38"/>
+      <x:c r="G156" s="39" t="n">
         <x:f>SUM(G144:G155)</x:f>
         <x:v>267.39184624</x:v>
       </x:c>
-      <x:c r="H156" s="58" t="n">
+      <x:c r="H156" s="39" t="n">
         <x:f>SUM(H144:H155)</x:f>
         <x:v>297.1020513777778</x:v>
       </x:c>
-      <x:c r="I156" s="58" t="n">
+      <x:c r="I156" s="39" t="n">
         <x:f>SUM(I144:I155)</x:f>
         <x:v>29.710205137777784</x:v>
       </x:c>
-      <x:c r="J156" s="57"/>
-      <x:c r="K156" s="58" t="n">
+      <x:c r="J156" s="38"/>
+      <x:c r="K156" s="39" t="n">
         <x:f>SUM(K144:K155)</x:f>
         <x:v>29.710205137777784</x:v>
       </x:c>
-      <x:c r="L156" s="57"/>
+      <x:c r="L156" s="38"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -12969,8 +13007,8 @@
       <x:c r="O132" s="29"/>
       <x:c r="P132" s="29"/>
     </x:row>
-    <x:row r="135" ht="23" customHeight="1">
-      <x:c r="A135" s="46" t="str">
+    <x:row r="135" ht="15" customHeight="1">
+      <x:c r="A135" s="38" t="str">
         <x:v>PD 带宽争用耗时评估</x:v>
       </x:c>
       <x:c r="B135" s="29"/>
@@ -12985,7 +13023,7 @@
       <x:c r="K135" s="29"/>
       <x:c r="L135" s="29"/>
     </x:row>
-    <x:row r="136" ht="23" customHeight="1">
+    <x:row r="136" ht="15" customHeight="1">
       <x:c r="A136" s="29" t="str">
         <x:v>Decode 当前表参数；100 GB/s 为归一化示例。所列事件的带宽项，不等于完整 forward 耗时。</x:v>
       </x:c>
@@ -13001,29 +13039,29 @@
       <x:c r="K136" s="29"/>
       <x:c r="L136" s="29"/>
     </x:row>
-    <x:row r="137" ht="38" customHeight="1">
-      <x:c r="A137" s="49" t="str">
+    <x:row r="137" ht="30" customHeight="1">
+      <x:c r="A137" s="66" t="str">
         <x:v>带宽降幅</x:v>
       </x:c>
-      <x:c r="B137" s="49" t="str">
+      <x:c r="B137" s="66" t="str">
         <x:v>输入</x:v>
       </x:c>
-      <x:c r="C137" s="49" t="str">
+      <x:c r="C137" s="66" t="str">
         <x:v>争用覆盖率</x:v>
       </x:c>
-      <x:c r="D137" s="49" t="str">
+      <x:c r="D137" s="66" t="str">
         <x:v>输入</x:v>
       </x:c>
-      <x:c r="E137" s="49" t="str">
+      <x:c r="E137" s="66" t="str">
         <x:v>基线 forward ms</x:v>
       </x:c>
-      <x:c r="F137" s="49" t="str">
+      <x:c r="F137" s="66" t="str">
         <x:v>实测输入</x:v>
       </x:c>
-      <x:c r="G137" s="49" t="str">
+      <x:c r="G137" s="66" t="str">
         <x:v>默认带宽 GB/s</x:v>
       </x:c>
-      <x:c r="H137" s="49" t="str">
+      <x:c r="H137" s="66" t="str">
         <x:v>输入</x:v>
       </x:c>
       <x:c r="I137" s="29"/>
@@ -13031,19 +13069,19 @@
       <x:c r="K137" s="29"/>
       <x:c r="L137" s="29"/>
     </x:row>
-    <x:row r="138" ht="23" customHeight="1">
+    <x:row r="138" ht="15" customHeight="1">
       <x:c r="A138" s="29"/>
-      <x:c r="B138" s="51" t="n">
+      <x:c r="B138" s="67" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C138" s="29"/>
-      <x:c r="D138" s="51" t="n">
+      <x:c r="D138" s="67" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E138" s="29"/>
-      <x:c r="F138" s="52"/>
+      <x:c r="F138" s="68"/>
       <x:c r="G138" s="29"/>
-      <x:c r="H138" s="52" t="n">
+      <x:c r="H138" s="35" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="I138" s="29"/>
@@ -13051,45 +13089,45 @@
       <x:c r="K138" s="29"/>
       <x:c r="L138" s="29"/>
     </x:row>
-    <x:row r="139" ht="38" customHeight="1">
-      <x:c r="A139" s="49" t="str">
+    <x:row r="139" ht="30" customHeight="1">
+      <x:c r="A139" s="66" t="str">
         <x:v>通信基线 ms</x:v>
       </x:c>
-      <x:c r="B139" s="49" t="str">
+      <x:c r="B139" s="66" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="C139" s="49" t="str">
+      <x:c r="C139" s="66" t="str">
         <x:v>通信争用后 ms</x:v>
       </x:c>
-      <x:c r="D139" s="49" t="str">
+      <x:c r="D139" s="66" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="E139" s="49" t="str">
+      <x:c r="E139" s="66" t="str">
         <x:v>forward 增量 ms</x:v>
       </x:c>
-      <x:c r="F139" s="49" t="str">
+      <x:c r="F139" s="66" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="G139" s="49" t="str">
+      <x:c r="G139" s="66" t="str">
         <x:v>forward 新耗时 ms</x:v>
       </x:c>
-      <x:c r="H139" s="49" t="str">
+      <x:c r="H139" s="66" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="I139" s="49" t="str">
+      <x:c r="I139" s="66" t="str">
         <x:v>forward 增幅</x:v>
       </x:c>
-      <x:c r="J139" s="49" t="str">
+      <x:c r="J139" s="66" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="K139" s="49" t="str">
+      <x:c r="K139" s="66" t="str">
         <x:v>输入状态</x:v>
       </x:c>
-      <x:c r="L139" s="49" t="str">
+      <x:c r="L139" s="66" t="str">
         <x:v>状态</x:v>
       </x:c>
     </x:row>
-    <x:row r="140" ht="23" customHeight="1">
+    <x:row r="140" ht="15" customHeight="1">
       <x:c r="A140" s="53"/>
       <x:c r="B140" s="53" t="n">
         <x:f>SUM(G144:G155)</x:f>
@@ -13119,7 +13157,7 @@
         <x:v>待填基线</x:v>
       </x:c>
     </x:row>
-    <x:row r="141" ht="23" customHeight="1">
+    <x:row r="141" ht="15" customHeight="1">
       <x:c r="A141" s="29" t="str">
         <x:v>共享比例=0 表示独立链路；暴露系数=0 表示增量完全隐藏。默认均为 1，降幅只作用于带宽项。</x:v>
       </x:c>
@@ -13135,7 +13173,7 @@
       <x:c r="K141" s="29"/>
       <x:c r="L141" s="29"/>
     </x:row>
-    <x:row r="142" ht="23" customHeight="1">
+    <x:row r="142" ht="15" customHeight="1">
       <x:c r="A142" s="29" t="str">
         <x:v>V4.1 为 PD 条件评估；旧 KV 规划与新 main 的端到端迁移可用性未在本次验证。</x:v>
       </x:c>
@@ -13151,45 +13189,45 @@
       <x:c r="K142" s="29"/>
       <x:c r="L142" s="29"/>
     </x:row>
-    <x:row r="143" ht="38" customHeight="1">
-      <x:c r="A143" s="49" t="str">
+    <x:row r="143" ht="30" customHeight="1">
+      <x:c r="A143" s="66" t="str">
         <x:v>并行域</x:v>
       </x:c>
-      <x:c r="B143" s="49" t="str">
+      <x:c r="B143" s="66" t="str">
         <x:v>模块</x:v>
       </x:c>
-      <x:c r="C143" s="49" t="str">
+      <x:c r="C143" s="66" t="str">
         <x:v>通信事件</x:v>
       </x:c>
-      <x:c r="D143" s="49" t="str">
+      <x:c r="D143" s="66" t="str">
         <x:v>GB/Rank/Step</x:v>
       </x:c>
-      <x:c r="E143" s="49" t="str">
+      <x:c r="E143" s="66" t="str">
         <x:v>有效带宽 GB/s</x:v>
       </x:c>
-      <x:c r="F143" s="49" t="str">
+      <x:c r="F143" s="66" t="str">
         <x:v>共享比例</x:v>
       </x:c>
-      <x:c r="G143" s="49" t="str">
+      <x:c r="G143" s="66" t="str">
         <x:v>基线带宽项 ms</x:v>
       </x:c>
-      <x:c r="H143" s="49" t="str">
+      <x:c r="H143" s="66" t="str">
         <x:v>争用后带宽项 ms</x:v>
       </x:c>
-      <x:c r="I143" s="49" t="str">
+      <x:c r="I143" s="66" t="str">
         <x:v>通信增量 ms</x:v>
       </x:c>
-      <x:c r="J143" s="49" t="str">
+      <x:c r="J143" s="66" t="str">
         <x:v>暴露系数</x:v>
       </x:c>
-      <x:c r="K143" s="49" t="str">
+      <x:c r="K143" s="66" t="str">
         <x:v>forward 增量 ms</x:v>
       </x:c>
-      <x:c r="L143" s="49" t="str">
+      <x:c r="L143" s="66" t="str">
         <x:v>公式口径</x:v>
       </x:c>
     </x:row>
-    <x:row r="144" ht="23" customHeight="1">
+    <x:row r="144" ht="15" customHeight="1">
       <x:c r="A144" s="29" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -13203,11 +13241,11 @@
         <x:f>(K121*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E144" s="55" t="n">
+      <x:c r="E144" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F144" s="56" t="n">
+      <x:c r="F144" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G144" s="33" t="n">
@@ -13222,7 +13260,7 @@
         <x:f>G144*F144*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J144" s="56" t="n">
+      <x:c r="J144" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K144" s="33" t="n">
@@ -13233,7 +13271,7 @@
         <x:v>原通信行 121</x:v>
       </x:c>
     </x:row>
-    <x:row r="145" ht="23" customHeight="1">
+    <x:row r="145" ht="15" customHeight="1">
       <x:c r="A145" s="29" t="str">
         <x:v>DSA CP</x:v>
       </x:c>
@@ -13247,11 +13285,11 @@
         <x:f>(K122*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E145" s="55" t="n">
+      <x:c r="E145" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F145" s="56" t="n">
+      <x:c r="F145" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G145" s="33" t="n">
@@ -13266,7 +13304,7 @@
         <x:f>G145*F145*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J145" s="56" t="n">
+      <x:c r="J145" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K145" s="33" t="n">
@@ -13277,7 +13315,7 @@
         <x:v>原通信行 122</x:v>
       </x:c>
     </x:row>
-    <x:row r="146" ht="23" customHeight="1">
+    <x:row r="146" ht="15" customHeight="1">
       <x:c r="A146" s="29" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -13291,11 +13329,11 @@
         <x:f>(K123*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E146" s="55" t="n">
+      <x:c r="E146" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F146" s="56" t="n">
+      <x:c r="F146" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G146" s="33" t="n">
@@ -13310,7 +13348,7 @@
         <x:f>G146*F146*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J146" s="56" t="n">
+      <x:c r="J146" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K146" s="33" t="n">
@@ -13321,7 +13359,7 @@
         <x:v>原通信行 123</x:v>
       </x:c>
     </x:row>
-    <x:row r="147" ht="23" customHeight="1">
+    <x:row r="147" ht="15" customHeight="1">
       <x:c r="A147" s="29" t="str">
         <x:v>Attention TP</x:v>
       </x:c>
@@ -13335,11 +13373,11 @@
         <x:f>(K124*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E147" s="55" t="n">
+      <x:c r="E147" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F147" s="56" t="n">
+      <x:c r="F147" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G147" s="33" t="n">
@@ -13354,7 +13392,7 @@
         <x:f>G147*F147*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J147" s="56" t="n">
+      <x:c r="J147" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K147" s="33" t="n">
@@ -13365,7 +13403,7 @@
         <x:v>原通信行 124</x:v>
       </x:c>
     </x:row>
-    <x:row r="148" ht="23" customHeight="1">
+    <x:row r="148" ht="15" customHeight="1">
       <x:c r="A148" s="29" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -13379,11 +13417,11 @@
         <x:f>(K125*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E148" s="55" t="n">
+      <x:c r="E148" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F148" s="56" t="n">
+      <x:c r="F148" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G148" s="33" t="n">
@@ -13398,7 +13436,7 @@
         <x:f>G148*F148*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J148" s="56" t="n">
+      <x:c r="J148" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K148" s="33" t="n">
@@ -13409,7 +13447,7 @@
         <x:v>原通信行 125</x:v>
       </x:c>
     </x:row>
-    <x:row r="149" ht="23" customHeight="1">
+    <x:row r="149" ht="15" customHeight="1">
       <x:c r="A149" s="29" t="str">
         <x:v>EP 期望</x:v>
       </x:c>
@@ -13423,11 +13461,11 @@
         <x:f>(IF(F126=2,E126/5120*H126*(ROUNDUP((ROUNDUP(5120*F126/32,0)*32+32)/480,0)*512),NA()))/1e9</x:f>
         <x:v>0.33521664</x:v>
       </x:c>
-      <x:c r="E149" s="55" t="n">
+      <x:c r="E149" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F149" s="56" t="n">
+      <x:c r="F149" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G149" s="33" t="n">
@@ -13442,7 +13480,7 @@
         <x:f>G149*F149*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0.3724629333333334</x:v>
       </x:c>
-      <x:c r="J149" s="56" t="n">
+      <x:c r="J149" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K149" s="33" t="n">
@@ -13453,7 +13491,7 @@
         <x:v>原通信行 126</x:v>
       </x:c>
     </x:row>
-    <x:row r="150" ht="23" customHeight="1">
+    <x:row r="150" ht="15" customHeight="1">
       <x:c r="A150" s="29" t="str">
         <x:v>EP 期望</x:v>
       </x:c>
@@ -13467,11 +13505,11 @@
         <x:f>(IF(F127=2,K127*2^20+E127/5120*H127*32,NA()))/1e9</x:f>
         <x:v>0.30569472</x:v>
       </x:c>
-      <x:c r="E150" s="55" t="n">
+      <x:c r="E150" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F150" s="56" t="n">
+      <x:c r="F150" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G150" s="33" t="n">
@@ -13486,7 +13524,7 @@
         <x:f>G150*F150*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0.3396608</x:v>
       </x:c>
-      <x:c r="J150" s="56" t="n">
+      <x:c r="J150" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K150" s="33" t="n">
@@ -13497,7 +13535,7 @@
         <x:v>原通信行 127</x:v>
       </x:c>
     </x:row>
-    <x:row r="151" ht="23" customHeight="1">
+    <x:row r="151" ht="15" customHeight="1">
       <x:c r="A151" s="29" t="str">
         <x:v>Engram</x:v>
       </x:c>
@@ -13511,11 +13549,11 @@
         <x:f>(K128*2^20)/1e9</x:f>
         <x:v>0.000001008</x:v>
       </x:c>
-      <x:c r="E151" s="55" t="n">
+      <x:c r="E151" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F151" s="56" t="n">
+      <x:c r="F151" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G151" s="33" t="n">
@@ -13530,7 +13568,7 @@
         <x:f>G151*F151*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0.00000112</x:v>
       </x:c>
-      <x:c r="J151" s="56" t="n">
+      <x:c r="J151" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K151" s="33" t="n">
@@ -13541,7 +13579,7 @@
         <x:v>原通信行 128</x:v>
       </x:c>
     </x:row>
-    <x:row r="152" ht="23" customHeight="1">
+    <x:row r="152" ht="15" customHeight="1">
       <x:c r="A152" s="29" t="str">
         <x:v>Engram 期望</x:v>
       </x:c>
@@ -13555,11 +13593,11 @@
         <x:f>(K129*2^20)/1e9</x:f>
         <x:v>0.000043008</x:v>
       </x:c>
-      <x:c r="E152" s="55" t="n">
+      <x:c r="E152" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F152" s="56" t="n">
+      <x:c r="F152" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G152" s="33" t="n">
@@ -13574,7 +13612,7 @@
         <x:f>G152*F152*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0.000047786666666666674</x:v>
       </x:c>
-      <x:c r="J152" s="56" t="n">
+      <x:c r="J152" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K152" s="33" t="n">
@@ -13585,7 +13623,7 @@
         <x:v>原通信行 129</x:v>
       </x:c>
     </x:row>
-    <x:row r="153" ht="23" customHeight="1">
+    <x:row r="153" ht="15" customHeight="1">
       <x:c r="A153" s="29" t="str">
         <x:v>Engram 期望</x:v>
       </x:c>
@@ -13599,11 +13637,11 @@
         <x:f>(K130*2^20)/1e9</x:f>
         <x:v>0.002752512</x:v>
       </x:c>
-      <x:c r="E153" s="55" t="n">
+      <x:c r="E153" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F153" s="56" t="n">
+      <x:c r="F153" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G153" s="33" t="n">
@@ -13618,7 +13656,7 @@
         <x:f>G153*F153*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0.003058346666666667</x:v>
       </x:c>
-      <x:c r="J153" s="56" t="n">
+      <x:c r="J153" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K153" s="33" t="n">
@@ -13629,7 +13667,7 @@
         <x:v>原通信行 130</x:v>
       </x:c>
     </x:row>
-    <x:row r="154" ht="23" customHeight="1">
+    <x:row r="154" ht="15" customHeight="1">
       <x:c r="A154" s="29" t="str">
         <x:v>Engram</x:v>
       </x:c>
@@ -13643,11 +13681,11 @@
         <x:f>(K131*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E154" s="55" t="n">
+      <x:c r="E154" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F154" s="56" t="n">
+      <x:c r="F154" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G154" s="33" t="n">
@@ -13662,7 +13700,7 @@
         <x:f>G154*F154*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J154" s="56" t="n">
+      <x:c r="J154" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K154" s="33" t="n">
@@ -13673,7 +13711,7 @@
         <x:v>原通信行 131</x:v>
       </x:c>
     </x:row>
-    <x:row r="155" ht="23" customHeight="1">
+    <x:row r="155" ht="15" customHeight="1">
       <x:c r="A155" s="29" t="str">
         <x:v>EP</x:v>
       </x:c>
@@ -13687,11 +13725,11 @@
         <x:f>(IF(E126=0,0,H126*ROUNDUP(384/G126,0)*(G126-1)*32))/1e9</x:f>
         <x:v>0.00047616</x:v>
       </x:c>
-      <x:c r="E155" s="55" t="n">
+      <x:c r="E155" s="69" t="n">
         <x:f>$H$138</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F155" s="56" t="n">
+      <x:c r="F155" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G155" s="33" t="n">
@@ -13706,7 +13744,7 @@
         <x:f>G155*F155*$D$138*$B$138/(1-$B$138)</x:f>
         <x:v>0.0005290666666666667</x:v>
       </x:c>
-      <x:c r="J155" s="56" t="n">
+      <x:c r="J155" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K155" s="33" t="n">
@@ -13717,36 +13755,36 @@
         <x:v>额外控制量</x:v>
       </x:c>
     </x:row>
-    <x:row r="156" ht="23" customHeight="1">
-      <x:c r="A156" s="57" t="str">
+    <x:row r="156" ht="15" customHeight="1">
+      <x:c r="A156" s="38" t="str">
         <x:v>所列事件串行相加</x:v>
       </x:c>
-      <x:c r="B156" s="57"/>
-      <x:c r="C156" s="57"/>
-      <x:c r="D156" s="58" t="n">
+      <x:c r="B156" s="38"/>
+      <x:c r="C156" s="38"/>
+      <x:c r="D156" s="39" t="n">
         <x:f>SUM(D144:D155)</x:f>
         <x:v>0.6441840480000001</x:v>
       </x:c>
-      <x:c r="E156" s="58"/>
-      <x:c r="F156" s="57"/>
-      <x:c r="G156" s="58" t="n">
+      <x:c r="E156" s="38"/>
+      <x:c r="F156" s="38"/>
+      <x:c r="G156" s="39" t="n">
         <x:f>SUM(G144:G155)</x:f>
         <x:v>6.44184048</x:v>
       </x:c>
-      <x:c r="H156" s="58" t="n">
+      <x:c r="H156" s="39" t="n">
         <x:f>SUM(H144:H155)</x:f>
         <x:v>7.157600533333333</x:v>
       </x:c>
-      <x:c r="I156" s="58" t="n">
+      <x:c r="I156" s="39" t="n">
         <x:f>SUM(I144:I155)</x:f>
         <x:v>0.7157600533333335</x:v>
       </x:c>
-      <x:c r="J156" s="57"/>
-      <x:c r="K156" s="58" t="n">
+      <x:c r="J156" s="38"/>
+      <x:c r="K156" s="39" t="n">
         <x:f>SUM(K144:K155)</x:f>
         <x:v>0.7157600533333335</x:v>
       </x:c>
-      <x:c r="L156" s="57"/>
+      <x:c r="L156" s="38"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/models/deepseek-v4.1-flash/deepseek-v4.1-flash-analysis.xlsx
+++ b/models/deepseek-v4.1-flash/deepseek-v4.1-flash-analysis.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R06e8a5ad74f04336"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="Rc9500b8bc99845d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分钟场景" sheetId="3" r:id="R25b01de6de1643ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R2fd6dc433cb8485e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="Rd57c2a17fd2941ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分钟场景" sheetId="3" r:id="R6367f380f2b741b3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -381,7 +381,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -391,7 +391,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -401,7 +401,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -411,7 +411,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -6627,7 +6627,7 @@
     </x:row>
     <x:row r="142" ht="15" customHeight="1">
       <x:c r="A142" s="29" t="str">
-        <x:v>V4.1 为 PD 条件评估；旧 KV 规划与新 main 的端到端迁移可用性未在本次验证。</x:v>
+        <x:v>KV 字节按源码张量布局计算；计算口径见 analysis/PD-MINUTE.md。</x:v>
       </x:c>
       <x:c r="B142" s="29"/>
       <x:c r="C142" s="29"/>
@@ -13273,7 +13273,7 @@
     </x:row>
     <x:row r="142" ht="15" customHeight="1">
       <x:c r="A142" s="29" t="str">
-        <x:v>V4.1 为 PD 条件评估；旧 KV 规划与新 main 的端到端迁移可用性未在本次验证。</x:v>
+        <x:v>KV 字节按源码张量布局计算；计算口径见 analysis/PD-MINUTE.md。</x:v>
       </x:c>
       <x:c r="B142" s="29"/>
       <x:c r="C142" s="29"/>
@@ -14697,9 +14697,7 @@
         <x:f>$J$9</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O23" s="29" t="str">
-        <x:v>V4.1 KV 规划；运行未验证</x:v>
-      </x:c>
+      <x:c r="O23" s="29" t="str"/>
       <x:c r="P23" s="29"/>
       <x:c r="Q23" s="29"/>
       <x:c r="R23" s="29"/>
@@ -14760,7 +14758,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O24" s="29" t="str">
-        <x:v>V4.1 KV 规划；需 128 个冗余专家槽</x:v>
+        <x:v>需 128 个冗余专家槽</x:v>
       </x:c>
       <x:c r="P24" s="29"/>
       <x:c r="Q24" s="29"/>
@@ -14994,8 +14992,7 @@
         <x:v>0.01784768662115556</x:v>
       </x:c>
       <x:c r="O30" s="29" t="str">
-        <x:f>IF(W60="估算","估算；V4.1 规划",W60)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W60="估算","",W60)</x:f>
       </x:c>
       <x:c r="P30" s="53" t="n">
         <x:f>Q60</x:f>
@@ -15068,8 +15065,7 @@
         <x:v>0.00892384331057778</x:v>
       </x:c>
       <x:c r="O31" s="29" t="str">
-        <x:f>IF(W61="估算","估算；V4.1 规划",W61)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W61="估算","",W61)</x:f>
       </x:c>
       <x:c r="P31" s="53" t="n">
         <x:f>Q61</x:f>
@@ -15142,8 +15138,7 @@
         <x:v>0.00446192165528889</x:v>
       </x:c>
       <x:c r="O32" s="29" t="str">
-        <x:f>IF(W62="估算","估算；V4.1 规划",W62)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W62="估算","",W62)</x:f>
       </x:c>
       <x:c r="P32" s="53" t="n">
         <x:f>Q62</x:f>
@@ -15216,8 +15211,7 @@
         <x:v>0.0029746144368592593</x:v>
       </x:c>
       <x:c r="O33" s="29" t="str">
-        <x:f>IF(W63="估算","估算；V4.1 规划",W63)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W63="估算","",W63)</x:f>
       </x:c>
       <x:c r="P33" s="53" t="n">
         <x:f>Q63</x:f>
@@ -15290,8 +15284,7 @@
         <x:v>0.04743094165489779</x:v>
       </x:c>
       <x:c r="O34" s="29" t="str">
-        <x:f>IF(W64="估算","估算；V4.1 规划",W64)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W64="估算","",W64)</x:f>
       </x:c>
       <x:c r="P34" s="53" t="n">
         <x:f>Q64</x:f>
@@ -15364,8 +15357,7 @@
         <x:v>0.023715470827448897</x:v>
       </x:c>
       <x:c r="O35" s="29" t="str">
-        <x:f>IF(W65="估算","估算；V4.1 规划",W65)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W65="估算","",W65)</x:f>
       </x:c>
       <x:c r="P35" s="53" t="n">
         <x:f>Q65</x:f>
@@ -15438,8 +15430,7 @@
         <x:v>0.011857735413724448</x:v>
       </x:c>
       <x:c r="O36" s="29" t="str">
-        <x:f>IF(W66="估算","估算；V4.1 规划",W66)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W66="估算","",W66)</x:f>
       </x:c>
       <x:c r="P36" s="53" t="n">
         <x:f>Q66</x:f>
@@ -15512,8 +15503,7 @@
         <x:v>0.007905156942482965</x:v>
       </x:c>
       <x:c r="O37" s="29" t="str">
-        <x:f>IF(W67="估算","估算；V4.1 规划",W67)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W67="估算","",W67)</x:f>
       </x:c>
       <x:c r="P37" s="53" t="n">
         <x:f>Q67</x:f>
@@ -15586,8 +15576,7 @@
         <x:v>0.06259581183767705</x:v>
       </x:c>
       <x:c r="O38" s="29" t="str">
-        <x:f>IF(W68="估算","估算；V4.1 规划",W68)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W68="估算","",W68)</x:f>
       </x:c>
       <x:c r="P38" s="53" t="n">
         <x:f>Q68</x:f>
@@ -15660,8 +15649,7 @@
         <x:v>0.03129790591883853</x:v>
       </x:c>
       <x:c r="O39" s="29" t="str">
-        <x:f>IF(W69="估算","估算；V4.1 规划",W69)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W69="估算","",W69)</x:f>
       </x:c>
       <x:c r="P39" s="53" t="n">
         <x:f>Q69</x:f>
@@ -15734,8 +15722,7 @@
         <x:v>0.015648952959419263</x:v>
       </x:c>
       <x:c r="O40" s="29" t="str">
-        <x:f>IF(W70="估算","估算；V4.1 规划",W70)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W70="估算","",W70)</x:f>
       </x:c>
       <x:c r="P40" s="53" t="n">
         <x:f>Q70</x:f>
@@ -15808,8 +15795,7 @@
         <x:v>0.010432635306279508</x:v>
       </x:c>
       <x:c r="O41" s="29" t="str">
-        <x:f>IF(W71="估算","估算；V4.1 规划",W71)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W71="估算","",W71)</x:f>
       </x:c>
       <x:c r="P41" s="53" t="n">
         <x:f>Q71</x:f>
@@ -15882,8 +15868,7 @@
         <x:v>0.018351957820913582</x:v>
       </x:c>
       <x:c r="O42" s="29" t="str">
-        <x:f>IF(W72="估算","估算；V4.1 规划",W72)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W72="估算","",W72)</x:f>
       </x:c>
       <x:c r="P42" s="53" t="n">
         <x:f>Q72</x:f>
@@ -15956,8 +15941,7 @@
         <x:v>0.009175978910456791</x:v>
       </x:c>
       <x:c r="O43" s="29" t="str">
-        <x:f>IF(W73="估算","估算；V4.1 规划",W73)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W73="估算","",W73)</x:f>
       </x:c>
       <x:c r="P43" s="53" t="n">
         <x:f>Q73</x:f>
@@ -16030,8 +16014,7 @@
         <x:v>0.0045879894552283956</x:v>
       </x:c>
       <x:c r="O44" s="29" t="str">
-        <x:f>IF(W74="估算","估算；V4.1 规划",W74)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W74="估算","",W74)</x:f>
       </x:c>
       <x:c r="P44" s="53" t="n">
         <x:f>Q74</x:f>
@@ -16104,8 +16087,7 @@
         <x:v>0.00305865963681893</x:v>
       </x:c>
       <x:c r="O45" s="29" t="str">
-        <x:f>IF(W75="估算","估算；V4.1 规划",W75)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W75="估算","",W75)</x:f>
       </x:c>
       <x:c r="P45" s="53" t="n">
         <x:f>Q75</x:f>
@@ -16178,8 +16160,7 @@
         <x:v>0.04878097986640494</x:v>
       </x:c>
       <x:c r="O46" s="29" t="str">
-        <x:f>IF(W76="估算","估算；V4.1 规划",W76)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W76="估算","",W76)</x:f>
       </x:c>
       <x:c r="P46" s="53" t="n">
         <x:f>Q76</x:f>
@@ -16252,8 +16233,7 @@
         <x:v>0.02439048993320247</x:v>
       </x:c>
       <x:c r="O47" s="29" t="str">
-        <x:f>IF(W77="估算","估算；V4.1 规划",W77)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W77="估算","",W77)</x:f>
       </x:c>
       <x:c r="P47" s="53" t="n">
         <x:f>Q77</x:f>
@@ -16326,8 +16306,7 @@
         <x:v>0.012195244966601236</x:v>
       </x:c>
       <x:c r="O48" s="29" t="str">
-        <x:f>IF(W78="估算","估算；V4.1 规划",W78)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W78="估算","",W78)</x:f>
       </x:c>
       <x:c r="P48" s="53" t="n">
         <x:f>Q78</x:f>
@@ -16400,8 +16379,7 @@
         <x:v>0.008130163311067489</x:v>
       </x:c>
       <x:c r="O49" s="29" t="str">
-        <x:f>IF(W79="估算","估算；V4.1 规划",W79)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W79="估算","",W79)</x:f>
       </x:c>
       <x:c r="P49" s="53" t="n">
         <x:f>Q79</x:f>
@@ -16474,8 +16452,7 @@
         <x:v>0.06437828747783869</x:v>
       </x:c>
       <x:c r="O50" s="29" t="str">
-        <x:f>IF(W80="估算","估算；V4.1 规划",W80)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W80="估算","",W80)</x:f>
       </x:c>
       <x:c r="P50" s="53" t="n">
         <x:f>Q80</x:f>
@@ -16548,8 +16525,7 @@
         <x:v>0.032189143738919346</x:v>
       </x:c>
       <x:c r="O51" s="29" t="str">
-        <x:f>IF(W81="估算","估算；V4.1 规划",W81)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W81="估算","",W81)</x:f>
       </x:c>
       <x:c r="P51" s="53" t="n">
         <x:f>Q81</x:f>
@@ -16622,8 +16598,7 @@
         <x:v>0.016094571869459673</x:v>
       </x:c>
       <x:c r="O52" s="29" t="str">
-        <x:f>IF(W82="估算","估算；V4.1 规划",W82)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W82="估算","",W82)</x:f>
       </x:c>
       <x:c r="P52" s="53" t="n">
         <x:f>Q82</x:f>
@@ -16696,8 +16671,7 @@
         <x:v>0.01072971457963978</x:v>
       </x:c>
       <x:c r="O53" s="29" t="str">
-        <x:f>IF(W83="估算","估算；V4.1 规划",W83)</x:f>
-        <x:v>估算；V4.1 规划</x:v>
+        <x:f>IF(W83="估算","",W83)</x:f>
       </x:c>
       <x:c r="P53" s="53" t="n">
         <x:f>Q83</x:f>
@@ -19433,7 +19407,7 @@
         <x:v>保留行</x:v>
       </x:c>
       <x:c r="J89" s="78" t="str">
-        <x:v>取/规划行</x:v>
+        <x:v>取行</x:v>
       </x:c>
       <x:c r="K89" s="78" t="str">
         <x:v>生成 GiB</x:v>
@@ -19442,7 +19416,7 @@
         <x:v>保留 GiB</x:v>
       </x:c>
       <x:c r="M89" s="78" t="str">
-        <x:v>取/规划 GiB</x:v>
+        <x:v>取 GiB</x:v>
       </x:c>
       <x:c r="N89" s="29"/>
       <x:c r="O89" s="29"/>
@@ -20724,7 +20698,7 @@
     </x:row>
     <x:row r="114" ht="22" customHeight="1">
       <x:c r="A114" s="29" t="str">
-        <x:v>来源：库内 config.json、analysis/KV-EP-SPECS.md、analysis/PD-MINUTE.md；V4.1 为既有 KV 规划量。</x:v>
+        <x:v>来源：库内 config.json、analysis/KV-EP-SPECS.md、analysis/PD-MINUTE.md。</x:v>
       </x:c>
       <x:c r="B114" s="29"/>
       <x:c r="C114" s="29"/>

--- a/models/deepseek-v4.1-flash/deepseek-v4.1-flash-analysis.xlsx
+++ b/models/deepseek-v4.1-flash/deepseek-v4.1-flash-analysis.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R2fd6dc433cb8485e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="Rd57c2a17fd2941ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分钟场景" sheetId="3" r:id="R6367f380f2b741b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R60dc0e4a22f747f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="R7cad9cfc6d014626"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分钟场景" sheetId="3" r:id="R8d20362ba9c24296"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -150,7 +150,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="84">
+  <x:cellXfs count="85">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -350,6 +350,9 @@
     </x:xf>
     <x:xf numFmtId="211" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -14044,7 +14047,7 @@
       <x:c r="W4" s="29"/>
       <x:c r="X4" s="29"/>
     </x:row>
-    <x:row r="5" ht="22" customHeight="1">
+    <x:row r="5" ht="34" customHeight="1">
       <x:c r="A5" s="29" t="str">
         <x:v>每 P DP 请求数</x:v>
       </x:c>
@@ -14053,16 +14056,18 @@
       </x:c>
       <x:c r="C5" s="29"/>
       <x:c r="D5" s="29"/>
-      <x:c r="E5" s="29" t="str">
-        <x:v>P EP 组数</x:v>
+      <x:c r="E5" s="40" t="str">
+        <x:v>P deployment
+count</x:v>
       </x:c>
       <x:c r="F5" s="71" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="29"/>
       <x:c r="H5" s="29"/>
-      <x:c r="I5" s="29" t="str">
-        <x:v>D EP 组数</x:v>
+      <x:c r="I5" s="40" t="str">
+        <x:v>D deployment
+count</x:v>
       </x:c>
       <x:c r="J5" s="71" t="n">
         <x:v>1</x:v>
@@ -14180,25 +14185,28 @@
       <x:c r="W8" s="29"/>
       <x:c r="X8" s="29"/>
     </x:row>
-    <x:row r="9" ht="22" customHeight="1">
-      <x:c r="A9" s="29" t="str">
-        <x:v>每周期错峰批数</x:v>
+    <x:row r="9" ht="34" customHeight="1">
+      <x:c r="A9" s="40" t="str">
+        <x:v>KV bursts
+per interval</x:v>
       </x:c>
       <x:c r="B9" s="71" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C9" s="29"/>
       <x:c r="D9" s="29"/>
-      <x:c r="E9" s="29" t="str">
-        <x:v>通信共享比例</x:v>
+      <x:c r="E9" s="40" t="str">
+        <x:v>EP shared
+resource fraction</x:v>
       </x:c>
       <x:c r="F9" s="73" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="29"/>
       <x:c r="H9" s="29"/>
-      <x:c r="I9" s="29" t="str">
-        <x:v>关键路径暴露率</x:v>
+      <x:c r="I9" s="40" t="str">
+        <x:v>EP exposed
+comm fraction</x:v>
       </x:c>
       <x:c r="J9" s="73" t="n">
         <x:v>1</x:v>
@@ -14256,9 +14264,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C11" s="29"/>
-      <x:c r="D11" s="29" t="str">
-        <x:v>TTFT 暂作 P 批次间隔；步间隔＝TPOT×平均产出。每周期 1 批表示各 P DP 同步交接。</x:v>
-      </x:c>
+      <x:c r="D11" s="29" t="str"/>
       <x:c r="E11" s="29"/>
       <x:c r="F11" s="29"/>
       <x:c r="G11" s="29"/>
@@ -14281,7 +14287,9 @@
       <x:c r="X11" s="29"/>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="29"/>
+      <x:c r="A12" s="29" t="str">
+        <x:v>P = Prefill，D = Decode。通常只需修改带宽、请求数和 TTFT/TPOT；附加假设可保持默认。</x:v>
+      </x:c>
       <x:c r="B12" s="29"/>
       <x:c r="C12" s="29"/>
       <x:c r="D12" s="29"/>
@@ -14307,7 +14315,9 @@
       <x:c r="X12" s="29"/>
     </x:row>
     <x:row r="13" ht="22" customHeight="1">
-      <x:c r="A13" s="29"/>
+      <x:c r="A13" s="29" t="str">
+        <x:v>Total overhead 表示基线 60 秒工作量的额外耗时；TTFT 在这里作为 KV 批次到达间隔。</x:v>
+      </x:c>
       <x:c r="B13" s="29"/>
       <x:c r="C13" s="29"/>
       <x:c r="D13" s="29"/>
@@ -14386,22 +14396,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G15" s="29"/>
-      <x:c r="H15" s="29" t="str">
-        <x:v>黄色为输入；模型 / EP 带宽可在下表逐项覆盖。</x:v>
-      </x:c>
-      <x:c r="I15" s="29"/>
-      <x:c r="J15" s="29"/>
-      <x:c r="K15" s="29"/>
-      <x:c r="L15" s="29"/>
-      <x:c r="M15" s="29"/>
-      <x:c r="N15" s="29"/>
-      <x:c r="O15" s="29"/>
-      <x:c r="P15" s="29"/>
-      <x:c r="Q15" s="29"/>
-      <x:c r="R15" s="29"/>
-      <x:c r="S15" s="29"/>
-      <x:c r="T15" s="29"/>
-      <x:c r="U15" s="29"/>
+      <x:c r="H15" s="84" t="str">
+        <x:v>Default: P = D = 1; KV bursts = 1; shared / exposed fractions = 100%.</x:v>
+      </x:c>
+      <x:c r="I15" s="84"/>
+      <x:c r="J15" s="84"/>
+      <x:c r="K15" s="84"/>
+      <x:c r="L15" s="84"/>
+      <x:c r="M15" s="84"/>
+      <x:c r="N15" s="84"/>
+      <x:c r="O15" s="84"/>
+      <x:c r="P15" s="84"/>
+      <x:c r="Q15" s="84"/>
+      <x:c r="R15" s="84"/>
+      <x:c r="S15" s="84"/>
+      <x:c r="T15" s="84"/>
+      <x:c r="U15" s="84"/>
       <x:c r="V15" s="29"/>
       <x:c r="W15" s="29"/>
       <x:c r="X15" s="29"/>
@@ -14424,22 +14434,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G16" s="29"/>
-      <x:c r="H16" s="29" t="str">
-        <x:v>时间增量针对基线 60 秒工作量；不表示实测吞吐或 P99。</x:v>
-      </x:c>
-      <x:c r="I16" s="29"/>
-      <x:c r="J16" s="29"/>
-      <x:c r="K16" s="29"/>
-      <x:c r="L16" s="29"/>
-      <x:c r="M16" s="29"/>
-      <x:c r="N16" s="29"/>
-      <x:c r="O16" s="29"/>
-      <x:c r="P16" s="29"/>
-      <x:c r="Q16" s="29"/>
-      <x:c r="R16" s="29"/>
-      <x:c r="S16" s="29"/>
-      <x:c r="T16" s="29"/>
-      <x:c r="U16" s="29"/>
+      <x:c r="H16" s="84" t="str">
+        <x:v>Deployment count：完整 EP 部署的套数；EP32 每套 32 卡，EP256 每套 256 卡。</x:v>
+      </x:c>
+      <x:c r="I16" s="84"/>
+      <x:c r="J16" s="84"/>
+      <x:c r="K16" s="84"/>
+      <x:c r="L16" s="84"/>
+      <x:c r="M16" s="84"/>
+      <x:c r="N16" s="84"/>
+      <x:c r="O16" s="84"/>
+      <x:c r="P16" s="84"/>
+      <x:c r="Q16" s="84"/>
+      <x:c r="R16" s="84"/>
+      <x:c r="S16" s="84"/>
+      <x:c r="T16" s="84"/>
+      <x:c r="U16" s="84"/>
       <x:c r="V16" s="29"/>
       <x:c r="W16" s="29"/>
       <x:c r="X16" s="29"/>
@@ -14462,22 +14472,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G17" s="29"/>
-      <x:c r="H17" s="29" t="str">
-        <x:v>TTFT 只用于到达节奏，本页估算 D 侧 TPOT；P 耗时仍见原表。</x:v>
-      </x:c>
-      <x:c r="I17" s="29"/>
-      <x:c r="J17" s="29"/>
-      <x:c r="K17" s="29"/>
-      <x:c r="L17" s="29"/>
-      <x:c r="M17" s="29"/>
-      <x:c r="N17" s="29"/>
-      <x:c r="O17" s="29"/>
-      <x:c r="P17" s="29"/>
-      <x:c r="Q17" s="29"/>
-      <x:c r="R17" s="29"/>
-      <x:c r="S17" s="29"/>
-      <x:c r="T17" s="29"/>
-      <x:c r="U17" s="29"/>
+      <x:c r="H17" s="84" t="str">
+        <x:v>Shared resource fraction：通信中与 KV 竞争同一资源的比例。100% = 全部；0% = 资源独立。</x:v>
+      </x:c>
+      <x:c r="I17" s="84"/>
+      <x:c r="J17" s="84"/>
+      <x:c r="K17" s="84"/>
+      <x:c r="L17" s="84"/>
+      <x:c r="M17" s="84"/>
+      <x:c r="N17" s="84"/>
+      <x:c r="O17" s="84"/>
+      <x:c r="P17" s="84"/>
+      <x:c r="Q17" s="84"/>
+      <x:c r="R17" s="84"/>
+      <x:c r="S17" s="84"/>
+      <x:c r="T17" s="84"/>
+      <x:c r="U17" s="84"/>
       <x:c r="V17" s="29"/>
       <x:c r="W17" s="29"/>
       <x:c r="X17" s="29"/>
@@ -14494,22 +14504,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="G18" s="29"/>
-      <x:c r="H18" s="29" t="str">
-        <x:v>全 EP＝该步所有等效 EP 通信段都在 KV 窗口内；不代表整步持续时间都重叠。</x:v>
-      </x:c>
-      <x:c r="I18" s="29"/>
-      <x:c r="J18" s="29"/>
-      <x:c r="K18" s="29"/>
-      <x:c r="L18" s="29"/>
-      <x:c r="M18" s="29"/>
-      <x:c r="N18" s="29"/>
-      <x:c r="O18" s="29"/>
-      <x:c r="P18" s="29"/>
-      <x:c r="Q18" s="29"/>
-      <x:c r="R18" s="29"/>
-      <x:c r="S18" s="29"/>
-      <x:c r="T18" s="29"/>
-      <x:c r="U18" s="29"/>
+      <x:c r="H18" s="84" t="str">
+        <x:v>Exposed communication fraction：通信增时最终计入 forward 的比例；被计算遮住的部分不计入。</x:v>
+      </x:c>
+      <x:c r="I18" s="84"/>
+      <x:c r="J18" s="84"/>
+      <x:c r="K18" s="84"/>
+      <x:c r="L18" s="84"/>
+      <x:c r="M18" s="84"/>
+      <x:c r="N18" s="84"/>
+      <x:c r="O18" s="84"/>
+      <x:c r="P18" s="84"/>
+      <x:c r="Q18" s="84"/>
+      <x:c r="R18" s="84"/>
+      <x:c r="S18" s="84"/>
+      <x:c r="T18" s="84"/>
+      <x:c r="U18" s="84"/>
       <x:c r="V18" s="29"/>
       <x:c r="W18" s="29"/>
       <x:c r="X18" s="29"/>
@@ -14522,20 +14532,22 @@
       <x:c r="E19" s="29"/>
       <x:c r="F19" s="29"/>
       <x:c r="G19" s="29"/>
-      <x:c r="H19" s="29"/>
-      <x:c r="I19" s="29"/>
-      <x:c r="J19" s="29"/>
-      <x:c r="K19" s="29"/>
-      <x:c r="L19" s="29"/>
-      <x:c r="M19" s="29"/>
-      <x:c r="N19" s="29"/>
-      <x:c r="O19" s="29"/>
-      <x:c r="P19" s="29"/>
-      <x:c r="Q19" s="29"/>
-      <x:c r="R19" s="29"/>
-      <x:c r="S19" s="29"/>
-      <x:c r="T19" s="29"/>
-      <x:c r="U19" s="29"/>
+      <x:c r="H19" s="84" t="str">
+        <x:v>KV bursts per interval：一批 KV 均分成 m 次、等间隔发送；m = 2 时每次一半，总量不变。</x:v>
+      </x:c>
+      <x:c r="I19" s="84"/>
+      <x:c r="J19" s="84"/>
+      <x:c r="K19" s="84"/>
+      <x:c r="L19" s="84"/>
+      <x:c r="M19" s="84"/>
+      <x:c r="N19" s="84"/>
+      <x:c r="O19" s="84"/>
+      <x:c r="P19" s="84"/>
+      <x:c r="Q19" s="84"/>
+      <x:c r="R19" s="84"/>
+      <x:c r="S19" s="84"/>
+      <x:c r="T19" s="84"/>
+      <x:c r="U19" s="84"/>
       <x:c r="V19" s="29"/>
       <x:c r="W19" s="29"/>
       <x:c r="X19" s="29"/>
@@ -14548,20 +14560,22 @@
       <x:c r="E20" s="29"/>
       <x:c r="F20" s="29"/>
       <x:c r="G20" s="29"/>
-      <x:c r="H20" s="29"/>
-      <x:c r="I20" s="29"/>
-      <x:c r="J20" s="29"/>
-      <x:c r="K20" s="29"/>
-      <x:c r="L20" s="29"/>
-      <x:c r="M20" s="29"/>
-      <x:c r="N20" s="29"/>
-      <x:c r="O20" s="29"/>
-      <x:c r="P20" s="29"/>
-      <x:c r="Q20" s="29"/>
-      <x:c r="R20" s="29"/>
-      <x:c r="S20" s="29"/>
-      <x:c r="T20" s="29"/>
-      <x:c r="U20" s="29"/>
+      <x:c r="H20" s="84" t="str">
+        <x:v>Temporal overlap 由 KV 窗口自动计算；没有 profiling 时，不必另猜 shared / exposed 两个比例。</x:v>
+      </x:c>
+      <x:c r="I20" s="84"/>
+      <x:c r="J20" s="84"/>
+      <x:c r="K20" s="84"/>
+      <x:c r="L20" s="84"/>
+      <x:c r="M20" s="84"/>
+      <x:c r="N20" s="84"/>
+      <x:c r="O20" s="84"/>
+      <x:c r="P20" s="84"/>
+      <x:c r="Q20" s="84"/>
+      <x:c r="R20" s="84"/>
+      <x:c r="S20" s="84"/>
+      <x:c r="T20" s="84"/>
+      <x:c r="U20" s="84"/>
       <x:c r="V20" s="29"/>
       <x:c r="W20" s="29"/>
       <x:c r="X20" s="29"/>
@@ -14629,11 +14643,13 @@
       <x:c r="L22" s="78" t="str">
         <x:v>产出 tokens/步</x:v>
       </x:c>
-      <x:c r="M22" s="78" t="str">
-        <x:v>共享比例</x:v>
-      </x:c>
-      <x:c r="N22" s="78" t="str">
-        <x:v>暴露率</x:v>
+      <x:c r="M22" s="18" t="str">
+        <x:v>EP shared
+resource fraction</x:v>
+      </x:c>
+      <x:c r="N22" s="18" t="str">
+        <x:v>EP exposed
+comm fraction</x:v>
       </x:c>
       <x:c r="O22" s="78" t="str">
         <x:v>配置条件</x:v>
@@ -14910,8 +14926,9 @@
       <x:c r="K29" s="78" t="str">
         <x:v>重叠层调用 次/min</x:v>
       </x:c>
-      <x:c r="L29" s="78" t="str">
-        <x:v>60s 工作增时 ms</x:v>
+      <x:c r="L29" s="18" t="str">
+        <x:v>Total overhead
+ms/60s</x:v>
       </x:c>
       <x:c r="M29" s="78" t="str">
         <x:v>平均 TPOT 增量 μs</x:v>
@@ -16884,8 +16901,9 @@
       <x:c r="U59" s="78" t="str">
         <x:v>基线 FW/min</x:v>
       </x:c>
-      <x:c r="V59" s="78" t="str">
-        <x:v>60s 工作增时 ms</x:v>
+      <x:c r="V59" s="18" t="str">
+        <x:v>Total overhead
+ms/60s</x:v>
       </x:c>
       <x:c r="W59" s="78" t="str">
         <x:v>输入 / 调度状态</x:v>

--- a/models/deepseek-v4.1-flash/deepseek-v4.1-flash-analysis.xlsx
+++ b/models/deepseek-v4.1-flash/deepseek-v4.1-flash-analysis.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R60dc0e4a22f747f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="R7cad9cfc6d014626"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分钟场景" sheetId="3" r:id="R8d20362ba9c24296"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="Ra0c6ed5e64ad4770"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="Ra228353074844f12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分钟场景" sheetId="3" r:id="Reb5c54cfcb8744d8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,7 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="13">
+  <x:numFmts count="15">
     <x:numFmt numFmtId="200" formatCode="0.##"/>
     <x:numFmt numFmtId="201" formatCode="0.0000"/>
     <x:numFmt numFmtId="202" formatCode="#,##0.####"/>
@@ -29,6 +29,8 @@
     <x:numFmt numFmtId="210" formatCode="#,##0.000"/>
     <x:numFmt numFmtId="211" formatCode="#,##0.000000"/>
     <x:numFmt numFmtId="212" formatCode="0.000000%"/>
+    <x:numFmt numFmtId="213" formatCode="0.00000000%"/>
+    <x:numFmt numFmtId="214" formatCode="[=0]0.000000%;[&lt;0.00000001]&quot;&lt;0.000001%&quot;;0.000000%"/>
   </x:numFmts>
   <x:fonts count="6">
     <x:font>
@@ -63,7 +65,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="11">
+  <x:fills count="13">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -115,6 +117,16 @@
         <x:fgColor rgb="FFD9E2F3"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="3">
     <x:border/>
@@ -150,7 +162,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="85">
+  <x:cellXfs count="93">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -353,6 +365,30 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="213" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="214" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -13929,7 +13965,7 @@
     <x:col min="14" max="14" width="15" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="30" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="21" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="18" hidden="0" customWidth="1"/>
     <x:col min="20" max="20" width="18" hidden="0" customWidth="1"/>
@@ -14942,7 +14978,10 @@
       <x:c r="P29" s="78" t="str">
         <x:v>最低 EP GB/s</x:v>
       </x:c>
-      <x:c r="Q29" s="29"/>
+      <x:c r="Q29" s="91" t="str">
+        <x:v>Decode throughput
+loss (%)</x:v>
+      </x:c>
       <x:c r="R29" s="29"/>
       <x:c r="S29" s="29"/>
       <x:c r="T29" s="29"/>
@@ -15015,7 +15054,10 @@
         <x:f>Q60</x:f>
         <x:v>128.277504</x:v>
       </x:c>
-      <x:c r="Q30" s="29"/>
+      <x:c r="Q30" s="92" t="n">
+        <x:f>IF(ISNUMBER(L30),L30/(60000+L30),IF(L30="","",L30))</x:f>
+        <x:v>1.7847686302615647e-8</x:v>
+      </x:c>
       <x:c r="R30" s="29"/>
       <x:c r="S30" s="29"/>
       <x:c r="T30" s="29"/>
@@ -15088,7 +15130,10 @@
         <x:f>Q61</x:f>
         <x:v>64.138752</x:v>
       </x:c>
-      <x:c r="Q31" s="29"/>
+      <x:c r="Q31" s="92" t="n">
+        <x:f>IF(ISNUMBER(L31),L31/(60000+L31),IF(L31="","",L31))</x:f>
+        <x:v>8.9238432309428e-9</x:v>
+      </x:c>
       <x:c r="R31" s="29"/>
       <x:c r="S31" s="29"/>
       <x:c r="T31" s="29"/>
@@ -15161,7 +15206,10 @@
         <x:f>Q62</x:f>
         <x:v>32.069376</x:v>
       </x:c>
-      <x:c r="Q32" s="29"/>
+      <x:c r="Q32" s="92" t="n">
+        <x:f>IF(ISNUMBER(L32),L32/(60000+L32),IF(L32="","",L32))</x:f>
+        <x:v>4.461921635380145e-9</x:v>
+      </x:c>
       <x:c r="R32" s="29"/>
       <x:c r="S32" s="29"/>
       <x:c r="T32" s="29"/>
@@ -15234,7 +15282,10 @@
         <x:f>Q63</x:f>
         <x:v>21.379584</x:v>
       </x:c>
-      <x:c r="Q33" s="29"/>
+      <x:c r="Q33" s="92" t="n">
+        <x:f>IF(ISNUMBER(L33),L33/(60000+L33),IF(L33="","",L33))</x:f>
+        <x:v>2.974614428010928e-9</x:v>
+      </x:c>
       <x:c r="R33" s="29"/>
       <x:c r="S33" s="29"/>
       <x:c r="T33" s="29"/>
@@ -15307,7 +15358,10 @@
         <x:f>Q64</x:f>
         <x:v>128.277504</x:v>
       </x:c>
-      <x:c r="Q34" s="29"/>
+      <x:c r="Q34" s="92" t="n">
+        <x:f>IF(ISNUMBER(L34),L34/(60000+L34),IF(L34="","",L34))</x:f>
+        <x:v>4.7430939405203674e-8</x:v>
+      </x:c>
       <x:c r="R34" s="29"/>
       <x:c r="S34" s="29"/>
       <x:c r="T34" s="29"/>
@@ -15380,7 +15434,10 @@
         <x:f>Q65</x:f>
         <x:v>64.138752</x:v>
       </x:c>
-      <x:c r="Q35" s="29"/>
+      <x:c r="Q35" s="92" t="n">
+        <x:f>IF(ISNUMBER(L35),L35/(60000+L35),IF(L35="","",L35))</x:f>
+        <x:v>2.3715470265025355e-8</x:v>
+      </x:c>
       <x:c r="R35" s="29"/>
       <x:c r="S35" s="29"/>
       <x:c r="T35" s="29"/>
@@ -15453,7 +15510,10 @@
         <x:f>Q66</x:f>
         <x:v>32.069376</x:v>
       </x:c>
-      <x:c r="Q36" s="29"/>
+      <x:c r="Q36" s="92" t="n">
+        <x:f>IF(ISNUMBER(L36),L36/(60000+L36),IF(L36="","",L36))</x:f>
+        <x:v>1.185773527311856e-8</x:v>
+      </x:c>
       <x:c r="R36" s="29"/>
       <x:c r="S36" s="29"/>
       <x:c r="T36" s="29"/>
@@ -15526,7 +15586,10 @@
         <x:f>Q67</x:f>
         <x:v>21.379584</x:v>
       </x:c>
-      <x:c r="Q37" s="29"/>
+      <x:c r="Q37" s="92" t="n">
+        <x:f>IF(ISNUMBER(L37),L37/(60000+L37),IF(L37="","",L37))</x:f>
+        <x:v>7.90515687999146e-9</x:v>
+      </x:c>
       <x:c r="R37" s="29"/>
       <x:c r="S37" s="29"/>
       <x:c r="T37" s="29"/>
@@ -15599,7 +15662,10 @@
         <x:f>Q68</x:f>
         <x:v>128.277504</x:v>
       </x:c>
-      <x:c r="Q38" s="29"/>
+      <x:c r="Q38" s="92" t="n">
+        <x:f>IF(ISNUMBER(L38),L38/(60000+L38),IF(L38="","",L38))</x:f>
+        <x:v>6.259580791944164e-8</x:v>
+      </x:c>
       <x:c r="R38" s="29"/>
       <x:c r="S38" s="29"/>
       <x:c r="T38" s="29"/>
@@ -15672,7 +15738,10 @@
         <x:f>Q69</x:f>
         <x:v>64.138752</x:v>
       </x:c>
-      <x:c r="Q39" s="29"/>
+      <x:c r="Q39" s="92" t="n">
+        <x:f>IF(ISNUMBER(L39),L39/(60000+L39),IF(L39="","",L39))</x:f>
+        <x:v>3.129790493927964e-8</x:v>
+      </x:c>
       <x:c r="R39" s="29"/>
       <x:c r="S39" s="29"/>
       <x:c r="T39" s="29"/>
@@ -15745,7 +15814,10 @@
         <x:f>Q70</x:f>
         <x:v>32.069376</x:v>
       </x:c>
-      <x:c r="Q40" s="29"/>
+      <x:c r="Q40" s="92" t="n">
+        <x:f>IF(ISNUMBER(L40),L40/(60000+L40),IF(L40="","",L40))</x:f>
+        <x:v>1.5648952714529536e-8</x:v>
+      </x:c>
       <x:c r="R40" s="29"/>
       <x:c r="S40" s="29"/>
       <x:c r="T40" s="29"/>
@@ -15818,7 +15890,10 @@
         <x:f>Q71</x:f>
         <x:v>21.379584</x:v>
       </x:c>
-      <x:c r="Q41" s="29"/>
+      <x:c r="Q41" s="92" t="n">
+        <x:f>IF(ISNUMBER(L41),L41/(60000+L41),IF(L41="","",L41))</x:f>
+        <x:v>1.0432635197439629e-8</x:v>
+      </x:c>
       <x:c r="R41" s="29"/>
       <x:c r="S41" s="29"/>
       <x:c r="T41" s="29"/>
@@ -15891,7 +15966,10 @@
         <x:f>Q72</x:f>
         <x:v>131.93088</x:v>
       </x:c>
-      <x:c r="Q42" s="29"/>
+      <x:c r="Q42" s="92" t="n">
+        <x:f>IF(ISNUMBER(L42),L42/(60000+L42),IF(L42="","",L42))</x:f>
+        <x:v>1.835195748411923e-8</x:v>
+      </x:c>
       <x:c r="R42" s="29"/>
       <x:c r="S42" s="29"/>
       <x:c r="T42" s="29"/>
@@ -15964,7 +16042,10 @@
         <x:f>Q73</x:f>
         <x:v>65.96544</x:v>
       </x:c>
-      <x:c r="Q43" s="29"/>
+      <x:c r="Q43" s="92" t="n">
+        <x:f>IF(ISNUMBER(L43),L43/(60000+L43),IF(L43="","",L43))</x:f>
+        <x:v>9.175978826258202e-9</x:v>
+      </x:c>
       <x:c r="R43" s="29"/>
       <x:c r="S43" s="29"/>
       <x:c r="T43" s="29"/>
@@ -16037,7 +16118,10 @@
         <x:f>Q74</x:f>
         <x:v>32.98272</x:v>
       </x:c>
-      <x:c r="Q44" s="29"/>
+      <x:c r="Q44" s="92" t="n">
+        <x:f>IF(ISNUMBER(L44),L44/(60000+L44),IF(L44="","",L44))</x:f>
+        <x:v>4.587989434178748e-9</x:v>
+      </x:c>
       <x:c r="R44" s="29"/>
       <x:c r="S44" s="29"/>
       <x:c r="T44" s="29"/>
@@ -16110,7 +16194,10 @@
         <x:f>Q75</x:f>
         <x:v>21.98848</x:v>
       </x:c>
-      <x:c r="Q45" s="29"/>
+      <x:c r="Q45" s="92" t="n">
+        <x:f>IF(ISNUMBER(L45),L45/(60000+L45),IF(L45="","",L45))</x:f>
+        <x:v>3.0586596274635314e-9</x:v>
+      </x:c>
       <x:c r="R45" s="29"/>
       <x:c r="S45" s="29"/>
       <x:c r="T45" s="29"/>
@@ -16183,7 +16270,10 @@
         <x:f>Q76</x:f>
         <x:v>131.93088</x:v>
       </x:c>
-      <x:c r="Q46" s="29"/>
+      <x:c r="Q46" s="92" t="n">
+        <x:f>IF(ISNUMBER(L46),L46/(60000+L46),IF(L46="","",L46))</x:f>
+        <x:v>4.878097748682107e-8</x:v>
+      </x:c>
       <x:c r="R46" s="29"/>
       <x:c r="S46" s="29"/>
       <x:c r="T46" s="29"/>
@@ -16256,7 +16346,10 @@
         <x:f>Q77</x:f>
         <x:v>65.96544</x:v>
       </x:c>
-      <x:c r="Q47" s="29"/>
+      <x:c r="Q47" s="92" t="n">
+        <x:f>IF(ISNUMBER(L47),L47/(60000+L47),IF(L47="","",L47))</x:f>
+        <x:v>2.4390489338306487e-8</x:v>
+      </x:c>
       <x:c r="R47" s="29"/>
       <x:c r="S47" s="29"/>
       <x:c r="T47" s="29"/>
@@ -16329,7 +16422,10 @@
         <x:f>Q78</x:f>
         <x:v>32.98272</x:v>
       </x:c>
-      <x:c r="Q48" s="29"/>
+      <x:c r="Q48" s="92" t="n">
+        <x:f>IF(ISNUMBER(L48),L48/(60000+L48),IF(L48="","",L48))</x:f>
+        <x:v>1.2195244817877239e-8</x:v>
+      </x:c>
       <x:c r="R48" s="29"/>
       <x:c r="S48" s="29"/>
       <x:c r="T48" s="29"/>
@@ -16402,7 +16498,10 @@
         <x:f>Q79</x:f>
         <x:v>21.98848</x:v>
       </x:c>
-      <x:c r="Q49" s="29"/>
+      <x:c r="Q49" s="92" t="n">
+        <x:f>IF(ISNUMBER(L49),L49/(60000+L49),IF(L49="","",L49))</x:f>
+        <x:v>8.130163244967935e-9</x:v>
+      </x:c>
       <x:c r="R49" s="29"/>
       <x:c r="S49" s="29"/>
       <x:c r="T49" s="29"/>
@@ -16475,7 +16574,10 @@
         <x:f>Q80</x:f>
         <x:v>131.93088</x:v>
       </x:c>
-      <x:c r="Q50" s="29"/>
+      <x:c r="Q50" s="92" t="n">
+        <x:f>IF(ISNUMBER(L50),L50/(60000+L50),IF(L50="","",L50))</x:f>
+        <x:v>6.437828333327506e-8</x:v>
+      </x:c>
       <x:c r="R50" s="29"/>
       <x:c r="S50" s="29"/>
       <x:c r="T50" s="29"/>
@@ -16548,7 +16650,10 @@
         <x:f>Q81</x:f>
         <x:v>65.96544</x:v>
       </x:c>
-      <x:c r="Q51" s="29"/>
+      <x:c r="Q51" s="92" t="n">
+        <x:f>IF(ISNUMBER(L51),L51/(60000+L51),IF(L51="","",L51))</x:f>
+        <x:v>3.21891427027784e-8</x:v>
+      </x:c>
       <x:c r="R51" s="29"/>
       <x:c r="S51" s="29"/>
       <x:c r="T51" s="29"/>
@@ -16621,7 +16726,10 @@
         <x:f>Q82</x:f>
         <x:v>32.98272</x:v>
       </x:c>
-      <x:c r="Q52" s="29"/>
+      <x:c r="Q52" s="92" t="n">
+        <x:f>IF(ISNUMBER(L52),L52/(60000+L52),IF(L52="","",L52))</x:f>
+        <x:v>1.6094571610424433e-8</x:v>
+      </x:c>
       <x:c r="R52" s="29"/>
       <x:c r="S52" s="29"/>
       <x:c r="T52" s="29"/>
@@ -16694,7 +16802,10 @@
         <x:f>Q83</x:f>
         <x:v>21.98848</x:v>
       </x:c>
-      <x:c r="Q53" s="29"/>
+      <x:c r="Q53" s="92" t="n">
+        <x:f>IF(ISNUMBER(L53),L53/(60000+L53),IF(L53="","",L53))</x:f>
+        <x:v>1.0729714464513006e-8</x:v>
+      </x:c>
       <x:c r="R53" s="29"/>
       <x:c r="S53" s="29"/>
       <x:c r="T53" s="29"/>
@@ -16704,7 +16815,9 @@
       <x:c r="X53" s="29"/>
     </x:row>
     <x:row r="54" ht="22" customHeight="1">
-      <x:c r="A54" s="29"/>
+      <x:c r="A54" s="29" t="str">
+        <x:v>Decode throughput loss = Total overhead / (60000 + Total overhead). Fixed batch size and tokens/step; Decode stays busy.</x:v>
+      </x:c>
       <x:c r="B54" s="29"/>
       <x:c r="C54" s="29"/>
       <x:c r="D54" s="29"/>
